--- a/lg-com-status-dashboard/신호등-Article.xlsx
+++ b/lg-com-status-dashboard/신호등-Article.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="347">
   <si>
     <t>Title</t>
   </si>
@@ -446,9 +446,6 @@
   </si>
   <si>
     <t>How to read electrical label of your refrigerator</t>
-  </si>
-  <si>
-    <t>취소</t>
   </si>
   <si>
     <t>ice solution (TBD)</t>
@@ -3589,15 +3586,9 @@
       <c r="J29" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="K29" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="L29" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="M29" s="14" t="s">
-        <v>145</v>
-      </c>
+      <c r="K29" s="13"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
       <c r="N29" s="48" t="s">
         <v>54</v>
       </c>
@@ -3634,7 +3625,7 @@
         <v>51</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="25"/>
@@ -3680,7 +3671,7 @@
         <v>51</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="25"/>
@@ -3723,16 +3714,16 @@
     <row r="32">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="D32" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="D32" s="54" t="s">
+      <c r="E32" s="33" t="s">
         <v>150</v>
-      </c>
-      <c r="E32" s="33" t="s">
-        <v>151</v>
       </c>
       <c r="F32" s="22" t="s">
         <v>55</v>
@@ -3781,16 +3772,16 @@
     <row r="33">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C33" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="54" t="s">
+      <c r="E33" s="38" t="s">
         <v>153</v>
-      </c>
-      <c r="E33" s="38" t="s">
-        <v>154</v>
       </c>
       <c r="F33" s="22" t="s">
         <v>55</v>
@@ -3839,16 +3830,16 @@
     <row r="34">
       <c r="A34" s="10"/>
       <c r="B34" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C34" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D34" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="E34" s="38" t="s">
         <v>156</v>
-      </c>
-      <c r="E34" s="38" t="s">
-        <v>157</v>
       </c>
       <c r="F34" s="22" t="s">
         <v>55</v>
@@ -3897,16 +3888,16 @@
     <row r="35">
       <c r="A35" s="10"/>
       <c r="B35" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C35" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="D35" s="54" t="s">
+      <c r="E35" s="38" t="s">
         <v>159</v>
-      </c>
-      <c r="E35" s="38" t="s">
-        <v>160</v>
       </c>
       <c r="F35" s="22" t="s">
         <v>55</v>
@@ -3955,16 +3946,16 @@
     <row r="36">
       <c r="A36" s="10"/>
       <c r="B36" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C36" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" s="54" t="s">
         <v>161</v>
       </c>
-      <c r="D36" s="54" t="s">
+      <c r="E36" s="38" t="s">
         <v>162</v>
-      </c>
-      <c r="E36" s="38" t="s">
-        <v>163</v>
       </c>
       <c r="F36" s="22" t="s">
         <v>55</v>
@@ -4013,13 +4004,13 @@
     <row r="37">
       <c r="A37" s="10"/>
       <c r="B37" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C37" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D37" s="54" t="s">
         <v>164</v>
-      </c>
-      <c r="D37" s="54" t="s">
-        <v>165</v>
       </c>
       <c r="E37" s="30" t="s">
         <v>54</v>
@@ -4028,7 +4019,7 @@
         <v>55</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H37" s="21" t="s">
         <v>56</v>
@@ -4071,13 +4062,13 @@
     <row r="38">
       <c r="A38" s="10"/>
       <c r="B38" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C38" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D38" s="54" t="s">
         <v>167</v>
-      </c>
-      <c r="D38" s="54" t="s">
-        <v>168</v>
       </c>
       <c r="E38" s="30" t="s">
         <v>54</v>
@@ -4086,7 +4077,7 @@
         <v>55</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H38" s="22" t="s">
         <v>55</v>
@@ -4131,13 +4122,13 @@
     <row r="39">
       <c r="A39" s="10"/>
       <c r="B39" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C39" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D39" s="54" t="s">
         <v>170</v>
-      </c>
-      <c r="D39" s="54" t="s">
-        <v>171</v>
       </c>
       <c r="E39" s="30" t="s">
         <v>54</v>
@@ -4146,7 +4137,7 @@
         <v>55</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H39" s="22" t="s">
         <v>55</v>
@@ -4191,13 +4182,13 @@
     <row r="40">
       <c r="A40" s="10"/>
       <c r="B40" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C40" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" s="54" t="s">
         <v>173</v>
-      </c>
-      <c r="D40" s="54" t="s">
-        <v>174</v>
       </c>
       <c r="E40" s="30" t="s">
         <v>54</v>
@@ -4206,7 +4197,7 @@
         <v>55</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H40" s="22" t="s">
         <v>55</v>
@@ -4249,13 +4240,13 @@
     <row r="41">
       <c r="A41" s="10"/>
       <c r="B41" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C41" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D41" s="54" t="s">
         <v>176</v>
-      </c>
-      <c r="D41" s="54" t="s">
-        <v>177</v>
       </c>
       <c r="E41" s="30" t="s">
         <v>54</v>
@@ -4264,7 +4255,7 @@
         <v>55</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H41" s="21" t="s">
         <v>56</v>
@@ -4309,13 +4300,13 @@
     <row r="42">
       <c r="A42" s="10"/>
       <c r="B42" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C42" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D42" s="54" t="s">
         <v>179</v>
-      </c>
-      <c r="D42" s="54" t="s">
-        <v>180</v>
       </c>
       <c r="E42" s="22" t="s">
         <v>55</v>
@@ -4324,7 +4315,7 @@
         <v>55</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H42" s="22" t="s">
         <v>55</v>
@@ -4367,10 +4358,10 @@
     <row r="43">
       <c r="A43" s="10"/>
       <c r="B43" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D43" s="25"/>
       <c r="E43" s="25"/>
@@ -4387,16 +4378,16 @@
       <c r="P43" s="16"/>
       <c r="Q43" s="23"/>
       <c r="R43" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="S43" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="S43" s="33" t="s">
+      <c r="T43" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="T43" s="33" t="s">
+      <c r="U43" s="38" t="s">
         <v>185</v>
-      </c>
-      <c r="U43" s="38" t="s">
-        <v>186</v>
       </c>
       <c r="V43" s="25"/>
       <c r="W43" s="25"/>
@@ -4421,10 +4412,10 @@
     <row r="44">
       <c r="A44" s="10"/>
       <c r="B44" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D44" s="25"/>
       <c r="E44" s="25"/>
@@ -4441,16 +4432,16 @@
       <c r="P44" s="16"/>
       <c r="Q44" s="23"/>
       <c r="R44" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="S44" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="S44" s="33" t="s">
+      <c r="T44" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="T44" s="33" t="s">
+      <c r="U44" s="38" t="s">
         <v>190</v>
-      </c>
-      <c r="U44" s="38" t="s">
-        <v>191</v>
       </c>
       <c r="V44" s="25"/>
       <c r="W44" s="25"/>
@@ -4475,10 +4466,10 @@
     <row r="45">
       <c r="A45" s="10"/>
       <c r="B45" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D45" s="25"/>
       <c r="E45" s="25"/>
@@ -4495,16 +4486,16 @@
       <c r="P45" s="16"/>
       <c r="Q45" s="23"/>
       <c r="R45" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="S45" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="S45" s="33" t="s">
+      <c r="T45" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="T45" s="33" t="s">
+      <c r="U45" s="38" t="s">
         <v>195</v>
-      </c>
-      <c r="U45" s="38" t="s">
-        <v>196</v>
       </c>
       <c r="V45" s="25"/>
       <c r="W45" s="25"/>
@@ -4529,10 +4520,10 @@
     <row r="46">
       <c r="A46" s="10"/>
       <c r="B46" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D46" s="25"/>
       <c r="E46" s="25"/>
@@ -4553,16 +4544,16 @@
       <c r="T46" s="25"/>
       <c r="U46" s="25"/>
       <c r="V46" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="W46" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="W46" s="33" t="s">
+      <c r="X46" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="X46" s="38" t="s">
+      <c r="Y46" s="38" t="s">
         <v>200</v>
-      </c>
-      <c r="Y46" s="38" t="s">
-        <v>201</v>
       </c>
       <c r="Z46" s="59" t="s">
         <v>55</v>
@@ -4585,10 +4576,10 @@
     <row r="47">
       <c r="A47" s="10"/>
       <c r="B47" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D47" s="35"/>
       <c r="E47" s="25"/>
@@ -4609,16 +4600,16 @@
       <c r="T47" s="25"/>
       <c r="U47" s="25"/>
       <c r="V47" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="W47" s="60" t="s">
         <v>203</v>
       </c>
-      <c r="W47" s="60" t="s">
+      <c r="X47" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="X47" s="38" t="s">
+      <c r="Y47" s="38" t="s">
         <v>205</v>
-      </c>
-      <c r="Y47" s="38" t="s">
-        <v>206</v>
       </c>
       <c r="Z47" s="22" t="s">
         <v>55</v>
@@ -4641,10 +4632,10 @@
     <row r="48">
       <c r="A48" s="10"/>
       <c r="B48" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D48" s="23"/>
       <c r="E48" s="25"/>
@@ -4665,16 +4656,16 @@
       <c r="T48" s="25"/>
       <c r="U48" s="25"/>
       <c r="V48" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="W48" s="60" t="s">
         <v>208</v>
       </c>
-      <c r="W48" s="60" t="s">
+      <c r="X48" s="38" t="s">
         <v>209</v>
       </c>
-      <c r="X48" s="38" t="s">
+      <c r="Y48" s="38" t="s">
         <v>210</v>
-      </c>
-      <c r="Y48" s="38" t="s">
-        <v>211</v>
       </c>
       <c r="Z48" s="22" t="s">
         <v>55</v>
@@ -4697,10 +4688,10 @@
     <row r="49">
       <c r="A49" s="10"/>
       <c r="B49" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D49" s="25"/>
       <c r="E49" s="25"/>
@@ -4721,16 +4712,16 @@
       <c r="T49" s="25"/>
       <c r="U49" s="25"/>
       <c r="V49" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="W49" s="60" t="s">
         <v>213</v>
       </c>
-      <c r="W49" s="60" t="s">
+      <c r="X49" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="X49" s="38" t="s">
+      <c r="Y49" s="38" t="s">
         <v>215</v>
-      </c>
-      <c r="Y49" s="38" t="s">
-        <v>216</v>
       </c>
       <c r="Z49" s="22" t="s">
         <v>55</v>
@@ -4753,10 +4744,10 @@
     <row r="50">
       <c r="A50" s="10"/>
       <c r="B50" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D50" s="25"/>
       <c r="E50" s="25"/>
@@ -4777,16 +4768,16 @@
       <c r="T50" s="25"/>
       <c r="U50" s="25"/>
       <c r="V50" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="W50" s="60" t="s">
         <v>218</v>
       </c>
-      <c r="W50" s="60" t="s">
+      <c r="X50" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="X50" s="38" t="s">
+      <c r="Y50" s="38" t="s">
         <v>220</v>
-      </c>
-      <c r="Y50" s="38" t="s">
-        <v>221</v>
       </c>
       <c r="Z50" s="22" t="s">
         <v>55</v>
@@ -4809,10 +4800,10 @@
     <row r="51">
       <c r="A51" s="10"/>
       <c r="B51" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D51" s="25"/>
       <c r="E51" s="35"/>
@@ -4833,16 +4824,16 @@
       <c r="T51" s="35"/>
       <c r="U51" s="35"/>
       <c r="V51" s="64" t="s">
+        <v>222</v>
+      </c>
+      <c r="W51" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="W51" s="65" t="s">
+      <c r="X51" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="X51" s="66" t="s">
+      <c r="Y51" s="66" t="s">
         <v>225</v>
-      </c>
-      <c r="Y51" s="66" t="s">
-        <v>226</v>
       </c>
       <c r="Z51" s="67" t="s">
         <v>55</v>
@@ -4865,10 +4856,10 @@
     <row r="52">
       <c r="A52" s="10"/>
       <c r="B52" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D52" s="26"/>
       <c r="E52" s="16"/>
@@ -4880,13 +4871,11 @@
         <v>55</v>
       </c>
       <c r="K52" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="L52" s="14"/>
+      <c r="M52" s="45" t="s">
         <v>228</v>
-      </c>
-      <c r="L52" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="M52" s="45" t="s">
-        <v>229</v>
       </c>
       <c r="N52" s="14" t="s">
         <v>54</v>
@@ -4921,10 +4910,10 @@
     <row r="53">
       <c r="A53" s="10"/>
       <c r="B53" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D53" s="26"/>
       <c r="E53" s="16"/>
@@ -4936,13 +4925,13 @@
         <v>55</v>
       </c>
       <c r="K53" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="L53" s="69" t="s">
         <v>231</v>
       </c>
-      <c r="L53" s="69" t="s">
+      <c r="M53" s="47" t="s">
         <v>232</v>
-      </c>
-      <c r="M53" s="47" t="s">
-        <v>233</v>
       </c>
       <c r="N53" s="14" t="s">
         <v>54</v>
@@ -4977,10 +4966,10 @@
     <row r="54">
       <c r="A54" s="10"/>
       <c r="B54" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D54" s="26"/>
       <c r="E54" s="16"/>
@@ -4992,13 +4981,13 @@
         <v>55</v>
       </c>
       <c r="K54" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L54" s="69" t="s">
         <v>235</v>
       </c>
-      <c r="L54" s="69" t="s">
+      <c r="M54" s="47" t="s">
         <v>236</v>
-      </c>
-      <c r="M54" s="47" t="s">
-        <v>237</v>
       </c>
       <c r="N54" s="14" t="s">
         <v>54</v>
@@ -5033,10 +5022,10 @@
     <row r="55">
       <c r="A55" s="10"/>
       <c r="B55" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D55" s="26"/>
       <c r="E55" s="16"/>
@@ -5048,13 +5037,13 @@
         <v>55</v>
       </c>
       <c r="K55" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="L55" s="69" t="s">
         <v>239</v>
       </c>
-      <c r="L55" s="69" t="s">
+      <c r="M55" s="47" t="s">
         <v>240</v>
-      </c>
-      <c r="M55" s="47" t="s">
-        <v>241</v>
       </c>
       <c r="N55" s="14" t="s">
         <v>54</v>
@@ -5089,10 +5078,10 @@
     <row r="56">
       <c r="A56" s="10"/>
       <c r="B56" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D56" s="26"/>
       <c r="E56" s="16"/>
@@ -5107,10 +5096,10 @@
         <v>55</v>
       </c>
       <c r="L56" s="47" t="s">
+        <v>242</v>
+      </c>
+      <c r="M56" s="47" t="s">
         <v>243</v>
-      </c>
-      <c r="M56" s="47" t="s">
-        <v>244</v>
       </c>
       <c r="N56" s="14" t="s">
         <v>54</v>
@@ -5145,10 +5134,10 @@
     <row r="57">
       <c r="A57" s="10"/>
       <c r="B57" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D57" s="26"/>
       <c r="E57" s="16"/>
@@ -5160,13 +5149,13 @@
         <v>55</v>
       </c>
       <c r="K57" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="L57" s="69" t="s">
         <v>246</v>
       </c>
-      <c r="L57" s="69" t="s">
+      <c r="M57" s="47" t="s">
         <v>247</v>
-      </c>
-      <c r="M57" s="47" t="s">
-        <v>248</v>
       </c>
       <c r="N57" s="14" t="s">
         <v>54</v>
@@ -5201,10 +5190,10 @@
     <row r="58">
       <c r="A58" s="10"/>
       <c r="B58" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D58" s="26"/>
       <c r="E58" s="16"/>
@@ -5219,10 +5208,10 @@
         <v>55</v>
       </c>
       <c r="L58" s="69" t="s">
+        <v>249</v>
+      </c>
+      <c r="M58" s="47" t="s">
         <v>250</v>
-      </c>
-      <c r="M58" s="47" t="s">
-        <v>251</v>
       </c>
       <c r="N58" s="14" t="s">
         <v>54</v>
@@ -5257,10 +5246,10 @@
     <row r="59">
       <c r="A59" s="10"/>
       <c r="B59" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D59" s="36"/>
       <c r="E59" s="16"/>
@@ -5272,13 +5261,13 @@
         <v>55</v>
       </c>
       <c r="K59" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="L59" s="46" t="s">
         <v>253</v>
       </c>
-      <c r="L59" s="46" t="s">
+      <c r="M59" s="47" t="s">
         <v>254</v>
-      </c>
-      <c r="M59" s="47" t="s">
-        <v>255</v>
       </c>
       <c r="N59" s="14" t="s">
         <v>54</v>
@@ -5313,14 +5302,14 @@
     <row r="60">
       <c r="A60" s="10"/>
       <c r="B60" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D60" s="70"/>
       <c r="E60" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F60" s="16"/>
       <c r="G60" s="16"/>
@@ -5361,10 +5350,10 @@
     <row r="61">
       <c r="A61" s="10"/>
       <c r="B61" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>54</v>
@@ -5388,7 +5377,7 @@
       </c>
       <c r="L61" s="16"/>
       <c r="M61" s="45" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N61" s="14" t="s">
         <v>54</v>
@@ -5408,7 +5397,7 @@
         <v>54</v>
       </c>
       <c r="W61" s="71" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="X61" s="16"/>
       <c r="Y61" s="16"/>
@@ -5417,16 +5406,16 @@
       </c>
       <c r="AA61" s="16"/>
       <c r="AB61" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC61" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="AC61" s="47" t="s">
+      <c r="AD61" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="AD61" s="12" t="s">
+      <c r="AE61" s="12" t="s">
         <v>263</v>
-      </c>
-      <c r="AE61" s="12" t="s">
-        <v>264</v>
       </c>
       <c r="AF61" s="14" t="s">
         <v>56</v>
@@ -5443,10 +5432,10 @@
     <row r="62">
       <c r="A62" s="10"/>
       <c r="B62" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
@@ -5489,10 +5478,10 @@
     <row r="63">
       <c r="A63" s="10"/>
       <c r="B63" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D63" s="72" t="s">
         <v>54</v>
@@ -5519,7 +5508,7 @@
         <v>56</v>
       </c>
       <c r="N63" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O63" s="62"/>
       <c r="P63" s="62"/>
@@ -5554,7 +5543,7 @@
         <v>54</v>
       </c>
       <c r="AE63" s="75" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AF63" s="62"/>
       <c r="AG63" s="76"/>
@@ -5569,10 +5558,10 @@
     <row r="64">
       <c r="A64" s="10"/>
       <c r="B64" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
@@ -5621,10 +5610,10 @@
     <row r="65">
       <c r="A65" s="10"/>
       <c r="B65" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C65" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="D65" s="16"/>
       <c r="E65" s="52"/>
@@ -5641,19 +5630,19 @@
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
       <c r="N65" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="O65" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="O65" s="12" t="s">
+      <c r="P65" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="P65" s="12" t="s">
+      <c r="Q65" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="Q65" s="12" t="s">
+      <c r="R65" s="10" t="s">
         <v>275</v>
-      </c>
-      <c r="R65" s="10" t="s">
-        <v>276</v>
       </c>
       <c r="S65" s="16"/>
       <c r="T65" s="16"/>
@@ -5664,12 +5653,8 @@
       <c r="Y65" s="16"/>
       <c r="Z65" s="16"/>
       <c r="AA65" s="16"/>
-      <c r="AB65" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC65" s="14" t="s">
-        <v>145</v>
-      </c>
+      <c r="AB65" s="14"/>
+      <c r="AC65" s="14"/>
       <c r="AD65" s="16"/>
       <c r="AE65" s="16"/>
       <c r="AF65" s="16"/>
@@ -5685,10 +5670,10 @@
     <row r="66">
       <c r="A66" s="10"/>
       <c r="B66" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
@@ -5705,19 +5690,19 @@
       <c r="L66" s="9"/>
       <c r="M66" s="77"/>
       <c r="N66" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="O66" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="O66" s="18" t="s">
+      <c r="P66" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="P66" s="18" t="s">
+      <c r="Q66" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="Q66" s="18" t="s">
-        <v>281</v>
-      </c>
       <c r="R66" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="S66" s="9"/>
       <c r="T66" s="9"/>
@@ -5729,13 +5714,13 @@
       <c r="Z66" s="9"/>
       <c r="AA66" s="9"/>
       <c r="AB66" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="AC66" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="AC66" s="18" t="s">
-        <v>283</v>
-      </c>
       <c r="AD66" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AE66" s="9"/>
       <c r="AF66" s="9"/>
@@ -5751,10 +5736,10 @@
     <row r="67">
       <c r="A67" s="10"/>
       <c r="B67" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
@@ -5771,19 +5756,19 @@
       <c r="L67" s="16"/>
       <c r="M67" s="79"/>
       <c r="N67" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="O67" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="O67" s="12" t="s">
+      <c r="P67" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="P67" s="12" t="s">
+      <c r="Q67" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="Q67" s="12" t="s">
-        <v>288</v>
-      </c>
       <c r="R67" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="S67" s="14"/>
       <c r="T67" s="16"/>
@@ -5794,12 +5779,8 @@
       <c r="Y67" s="16"/>
       <c r="Z67" s="14"/>
       <c r="AA67" s="16"/>
-      <c r="AB67" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC67" s="14" t="s">
-        <v>145</v>
-      </c>
+      <c r="AB67" s="14"/>
+      <c r="AC67" s="14"/>
       <c r="AD67" s="14"/>
       <c r="AE67" s="10"/>
       <c r="AF67" s="14"/>
@@ -5815,10 +5796,10 @@
     <row r="68">
       <c r="A68" s="10"/>
       <c r="B68" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
@@ -5856,12 +5837,8 @@
       <c r="Y68" s="27"/>
       <c r="Z68" s="14"/>
       <c r="AA68" s="27"/>
-      <c r="AB68" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC68" s="14" t="s">
-        <v>54</v>
-      </c>
+      <c r="AB68" s="14"/>
+      <c r="AC68" s="14"/>
       <c r="AD68" s="14"/>
       <c r="AE68" s="10"/>
       <c r="AF68" s="14"/>
@@ -5877,10 +5854,10 @@
     <row r="69">
       <c r="A69" s="10"/>
       <c r="B69" s="82" t="s">
+        <v>289</v>
+      </c>
+      <c r="C69" s="82" t="s">
         <v>290</v>
-      </c>
-      <c r="C69" s="82" t="s">
-        <v>291</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>56</v>
@@ -5904,7 +5881,7 @@
       </c>
       <c r="L69" s="16"/>
       <c r="M69" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N69" s="10" t="s">
         <v>56</v>
@@ -5924,10 +5901,10 @@
         <v>56</v>
       </c>
       <c r="W69" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="X69" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Y69" s="16"/>
       <c r="Z69" s="85" t="s">
@@ -5935,13 +5912,13 @@
       </c>
       <c r="AA69" s="16"/>
       <c r="AB69" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="AC69" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="AC69" s="15" t="s">
+      <c r="AD69" s="15" t="s">
         <v>295</v>
-      </c>
-      <c r="AD69" s="15" t="s">
-        <v>296</v>
       </c>
       <c r="AE69" s="10" t="s">
         <v>56</v>
@@ -5961,10 +5938,10 @@
     <row r="70">
       <c r="A70" s="10"/>
       <c r="B70" s="82" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C70" s="82" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D70" s="86" t="s">
         <v>56</v>
@@ -5988,7 +5965,7 @@
       </c>
       <c r="L70" s="16"/>
       <c r="M70" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N70" s="10" t="s">
         <v>56</v>
@@ -6008,10 +5985,10 @@
         <v>56</v>
       </c>
       <c r="W70" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="X70" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Y70" s="16"/>
       <c r="Z70" s="10" t="s">
@@ -6019,13 +5996,13 @@
       </c>
       <c r="AA70" s="27"/>
       <c r="AB70" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC70" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="AC70" s="15" t="s">
+      <c r="AD70" s="15" t="s">
         <v>301</v>
-      </c>
-      <c r="AD70" s="15" t="s">
-        <v>302</v>
       </c>
       <c r="AE70" s="10" t="s">
         <v>56</v>
@@ -6045,10 +6022,10 @@
     <row r="71">
       <c r="A71" s="10"/>
       <c r="B71" s="82" t="s">
+        <v>302</v>
+      </c>
+      <c r="C71" s="82" t="s">
         <v>303</v>
-      </c>
-      <c r="C71" s="82" t="s">
-        <v>304</v>
       </c>
       <c r="D71" s="88"/>
       <c r="E71" s="14"/>
@@ -6091,10 +6068,10 @@
     <row r="72">
       <c r="A72" s="10"/>
       <c r="B72" s="82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C72" s="82" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D72" s="93"/>
       <c r="E72" s="14"/>
@@ -6137,13 +6114,13 @@
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C73" s="82" t="s">
+        <v>305</v>
+      </c>
+      <c r="D73" s="95" t="s">
         <v>306</v>
-      </c>
-      <c r="D73" s="95" t="s">
-        <v>307</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>54</v>
@@ -6152,7 +6129,7 @@
         <v>54</v>
       </c>
       <c r="G73" s="47" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H73" s="14" t="s">
         <v>55</v>
@@ -6166,7 +6143,7 @@
       </c>
       <c r="L73" s="92"/>
       <c r="M73" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N73" s="14" t="s">
         <v>54</v>
@@ -6174,22 +6151,22 @@
       <c r="O73" s="49"/>
       <c r="P73" s="49"/>
       <c r="Q73" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="R73" s="96" t="s">
         <v>310</v>
       </c>
-      <c r="R73" s="96" t="s">
+      <c r="S73" s="96" t="s">
         <v>311</v>
       </c>
-      <c r="S73" s="96" t="s">
+      <c r="T73" s="47" t="s">
         <v>312</v>
       </c>
-      <c r="T73" s="47" t="s">
+      <c r="U73" s="47" t="s">
         <v>313</v>
       </c>
-      <c r="U73" s="47" t="s">
+      <c r="V73" s="12" t="s">
         <v>314</v>
-      </c>
-      <c r="V73" s="12" t="s">
-        <v>315</v>
       </c>
       <c r="W73" s="14" t="s">
         <v>56</v>
@@ -6199,25 +6176,25 @@
       <c r="Z73" s="92"/>
       <c r="AA73" s="89"/>
       <c r="AB73" s="47" t="s">
+        <v>315</v>
+      </c>
+      <c r="AC73" s="47" t="s">
         <v>316</v>
       </c>
-      <c r="AC73" s="47" t="s">
+      <c r="AD73" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="AE73" s="12" t="s">
         <v>317</v>
-      </c>
-      <c r="AD73" s="97" t="s">
-        <v>276</v>
-      </c>
-      <c r="AE73" s="12" t="s">
-        <v>318</v>
       </c>
       <c r="AF73" s="14" t="s">
         <v>56</v>
       </c>
       <c r="AG73" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="AH73" s="18" t="s">
         <v>319</v>
-      </c>
-      <c r="AH73" s="18" t="s">
-        <v>320</v>
       </c>
       <c r="AI73" s="9"/>
       <c r="AJ73" s="9"/>
@@ -6229,13 +6206,13 @@
     <row r="74">
       <c r="A74" s="9"/>
       <c r="B74" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C74" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="D74" s="18" t="s">
         <v>321</v>
-      </c>
-      <c r="D74" s="18" t="s">
-        <v>322</v>
       </c>
       <c r="E74" s="17" t="s">
         <v>54</v>
@@ -6244,7 +6221,7 @@
         <v>54</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>54</v>
@@ -6254,11 +6231,11 @@
         <v>54</v>
       </c>
       <c r="K74" s="18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L74" s="9"/>
       <c r="M74" s="18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N74" s="17" t="s">
         <v>54</v>
@@ -6266,19 +6243,19 @@
       <c r="O74" s="9"/>
       <c r="P74" s="9"/>
       <c r="Q74" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="R74" s="18" t="s">
         <v>326</v>
       </c>
-      <c r="R74" s="18" t="s">
+      <c r="S74" s="18" t="s">
         <v>327</v>
       </c>
-      <c r="S74" s="18" t="s">
+      <c r="T74" s="18" t="s">
         <v>328</v>
       </c>
-      <c r="T74" s="18" t="s">
+      <c r="U74" s="18" t="s">
         <v>329</v>
-      </c>
-      <c r="U74" s="18" t="s">
-        <v>330</v>
       </c>
       <c r="V74" s="17" t="s">
         <v>56</v>
@@ -6292,24 +6269,18 @@
       </c>
       <c r="Z74" s="9"/>
       <c r="AA74" s="9"/>
-      <c r="AB74" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC74" s="17" t="s">
-        <v>145</v>
-      </c>
+      <c r="AB74" s="17"/>
+      <c r="AC74" s="17"/>
       <c r="AD74" s="9"/>
-      <c r="AE74" s="17" t="s">
-        <v>145</v>
-      </c>
+      <c r="AE74" s="17"/>
       <c r="AF74" s="17" t="s">
         <v>56</v>
       </c>
       <c r="AG74" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="AH74" s="18" t="s">
         <v>331</v>
-      </c>
-      <c r="AH74" s="18" t="s">
-        <v>332</v>
       </c>
       <c r="AI74" s="9"/>
       <c r="AJ74" s="9"/>
@@ -6321,13 +6292,13 @@
     <row r="75" ht="18.0" customHeight="1">
       <c r="A75" s="9"/>
       <c r="B75" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C75" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="D75" s="18" t="s">
         <v>333</v>
-      </c>
-      <c r="D75" s="18" t="s">
-        <v>334</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>54</v>
@@ -6336,7 +6307,7 @@
         <v>54</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>54</v>
@@ -6346,11 +6317,11 @@
         <v>54</v>
       </c>
       <c r="K75" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L75" s="9"/>
       <c r="M75" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N75" s="17" t="s">
         <v>54</v>
@@ -6358,19 +6329,19 @@
       <c r="O75" s="9"/>
       <c r="P75" s="9"/>
       <c r="Q75" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="R75" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="R75" s="18" t="s">
+      <c r="S75" s="18" t="s">
         <v>339</v>
       </c>
-      <c r="S75" s="18" t="s">
+      <c r="T75" s="18" t="s">
         <v>340</v>
       </c>
-      <c r="T75" s="18" t="s">
+      <c r="U75" s="18" t="s">
         <v>341</v>
-      </c>
-      <c r="U75" s="18" t="s">
-        <v>342</v>
       </c>
       <c r="V75" s="17" t="s">
         <v>56</v>
@@ -6385,25 +6356,25 @@
       <c r="Z75" s="9"/>
       <c r="AA75" s="9"/>
       <c r="AB75" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="AC75" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="AC75" s="18" t="s">
+      <c r="AD75" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="AE75" s="18" t="s">
         <v>344</v>
-      </c>
-      <c r="AD75" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="AE75" s="18" t="s">
-        <v>345</v>
       </c>
       <c r="AF75" s="17" t="s">
         <v>56</v>
       </c>
       <c r="AG75" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="AH75" s="18" t="s">
         <v>346</v>
-      </c>
-      <c r="AH75" s="18" t="s">
-        <v>347</v>
       </c>
       <c r="AI75" s="9"/>
       <c r="AJ75" s="9"/>

--- a/lg-com-status-dashboard/신호등-Article.xlsx
+++ b/lg-com-status-dashboard/신호등-Article.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="349">
   <si>
     <t>Title</t>
   </si>
@@ -813,6 +813,12 @@
   <si>
     <t xml:space="preserve">https://www.lg.com/au/lg-experience/helpful-hints/washtower-myths-and-truths/
 </t>
+  </si>
+  <si>
+    <t>https://www.lg.com/ca_en/lg-experience/helpful-hints/washtower-myths-and-truths/</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/ca_fr/experience-lg/conseils-utiles/lg-experience-myths-and-truths-for-w/</t>
   </si>
   <si>
     <t>https://www.lg.com/in/magazine/lg-experience-2026-washtower-myths-and-truths/</t>
@@ -5533,17 +5539,17 @@
         <v>54</v>
       </c>
       <c r="AA63" s="62"/>
-      <c r="AB63" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC63" s="14" t="s">
-        <v>56</v>
+      <c r="AB63" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="AC63" s="12" t="s">
+        <v>268</v>
       </c>
       <c r="AD63" s="72" t="s">
         <v>54</v>
       </c>
       <c r="AE63" s="75" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AF63" s="62"/>
       <c r="AG63" s="76"/>
@@ -5561,7 +5567,7 @@
         <v>147</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
@@ -5610,10 +5616,10 @@
     <row r="65">
       <c r="A65" s="10"/>
       <c r="B65" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D65" s="16"/>
       <c r="E65" s="52"/>
@@ -5630,19 +5636,19 @@
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
       <c r="N65" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O65" s="12" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P65" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="R65" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="S65" s="16"/>
       <c r="T65" s="16"/>
@@ -5670,10 +5676,10 @@
     <row r="66">
       <c r="A66" s="10"/>
       <c r="B66" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
@@ -5690,19 +5696,19 @@
       <c r="L66" s="9"/>
       <c r="M66" s="77"/>
       <c r="N66" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="O66" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="P66" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q66" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="R66" s="17" t="s">
         <v>277</v>
-      </c>
-      <c r="O66" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="P66" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q66" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="R66" s="17" t="s">
-        <v>275</v>
       </c>
       <c r="S66" s="9"/>
       <c r="T66" s="9"/>
@@ -5714,13 +5720,13 @@
       <c r="Z66" s="9"/>
       <c r="AA66" s="9"/>
       <c r="AB66" s="18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AC66" s="18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AD66" s="17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AE66" s="9"/>
       <c r="AF66" s="9"/>
@@ -5736,10 +5742,10 @@
     <row r="67">
       <c r="A67" s="10"/>
       <c r="B67" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
@@ -5756,19 +5762,19 @@
       <c r="L67" s="16"/>
       <c r="M67" s="79"/>
       <c r="N67" s="12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O67" s="12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P67" s="12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="R67" s="14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="S67" s="14"/>
       <c r="T67" s="16"/>
@@ -5796,10 +5802,10 @@
     <row r="68">
       <c r="A68" s="10"/>
       <c r="B68" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
@@ -5854,10 +5860,10 @@
     <row r="69">
       <c r="A69" s="10"/>
       <c r="B69" s="82" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C69" s="82" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>56</v>
@@ -5881,7 +5887,7 @@
       </c>
       <c r="L69" s="16"/>
       <c r="M69" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N69" s="10" t="s">
         <v>56</v>
@@ -5901,10 +5907,10 @@
         <v>56</v>
       </c>
       <c r="W69" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="X69" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Y69" s="16"/>
       <c r="Z69" s="85" t="s">
@@ -5912,13 +5918,13 @@
       </c>
       <c r="AA69" s="16"/>
       <c r="AB69" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AC69" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AD69" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AE69" s="10" t="s">
         <v>56</v>
@@ -5938,10 +5944,10 @@
     <row r="70">
       <c r="A70" s="10"/>
       <c r="B70" s="82" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C70" s="82" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D70" s="86" t="s">
         <v>56</v>
@@ -5965,7 +5971,7 @@
       </c>
       <c r="L70" s="16"/>
       <c r="M70" s="15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N70" s="10" t="s">
         <v>56</v>
@@ -5985,10 +5991,10 @@
         <v>56</v>
       </c>
       <c r="W70" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="X70" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Y70" s="16"/>
       <c r="Z70" s="10" t="s">
@@ -5996,13 +6002,13 @@
       </c>
       <c r="AA70" s="27"/>
       <c r="AB70" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AC70" s="15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AD70" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AE70" s="10" t="s">
         <v>56</v>
@@ -6022,10 +6028,10 @@
     <row r="71">
       <c r="A71" s="10"/>
       <c r="B71" s="82" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C71" s="82" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D71" s="88"/>
       <c r="E71" s="14"/>
@@ -6068,10 +6074,10 @@
     <row r="72">
       <c r="A72" s="10"/>
       <c r="B72" s="82" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C72" s="82" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D72" s="93"/>
       <c r="E72" s="14"/>
@@ -6114,13 +6120,13 @@
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="82" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C73" s="82" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D73" s="95" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>54</v>
@@ -6129,7 +6135,7 @@
         <v>54</v>
       </c>
       <c r="G73" s="47" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H73" s="14" t="s">
         <v>55</v>
@@ -6143,7 +6149,7 @@
       </c>
       <c r="L73" s="92"/>
       <c r="M73" s="12" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N73" s="14" t="s">
         <v>54</v>
@@ -6151,22 +6157,22 @@
       <c r="O73" s="49"/>
       <c r="P73" s="49"/>
       <c r="Q73" s="12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="R73" s="96" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="S73" s="96" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="T73" s="47" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="U73" s="47" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="V73" s="12" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="W73" s="14" t="s">
         <v>56</v>
@@ -6176,25 +6182,25 @@
       <c r="Z73" s="92"/>
       <c r="AA73" s="89"/>
       <c r="AB73" s="47" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AC73" s="47" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AD73" s="97" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AE73" s="12" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AF73" s="14" t="s">
         <v>56</v>
       </c>
       <c r="AG73" s="18" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AH73" s="18" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AI73" s="9"/>
       <c r="AJ73" s="9"/>
@@ -6206,13 +6212,13 @@
     <row r="74">
       <c r="A74" s="9"/>
       <c r="B74" s="17" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E74" s="17" t="s">
         <v>54</v>
@@ -6221,7 +6227,7 @@
         <v>54</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>54</v>
@@ -6231,11 +6237,11 @@
         <v>54</v>
       </c>
       <c r="K74" s="18" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L74" s="9"/>
       <c r="M74" s="18" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N74" s="17" t="s">
         <v>54</v>
@@ -6243,19 +6249,19 @@
       <c r="O74" s="9"/>
       <c r="P74" s="9"/>
       <c r="Q74" s="18" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="R74" s="18" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="S74" s="18" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="T74" s="18" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="U74" s="18" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="V74" s="17" t="s">
         <v>56</v>
@@ -6277,10 +6283,10 @@
         <v>56</v>
       </c>
       <c r="AG74" s="18" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AH74" s="18" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AI74" s="9"/>
       <c r="AJ74" s="9"/>
@@ -6292,13 +6298,13 @@
     <row r="75" ht="18.0" customHeight="1">
       <c r="A75" s="9"/>
       <c r="B75" s="17" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>54</v>
@@ -6307,7 +6313,7 @@
         <v>54</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>54</v>
@@ -6317,11 +6323,11 @@
         <v>54</v>
       </c>
       <c r="K75" s="18" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L75" s="9"/>
       <c r="M75" s="18" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N75" s="17" t="s">
         <v>54</v>
@@ -6329,19 +6335,19 @@
       <c r="O75" s="9"/>
       <c r="P75" s="9"/>
       <c r="Q75" s="18" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R75" s="18" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S75" s="18" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="T75" s="18" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="U75" s="18" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="V75" s="17" t="s">
         <v>56</v>
@@ -6356,25 +6362,25 @@
       <c r="Z75" s="9"/>
       <c r="AA75" s="9"/>
       <c r="AB75" s="18" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AC75" s="18" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AD75" s="17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AE75" s="18" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AF75" s="17" t="s">
         <v>56</v>
       </c>
       <c r="AG75" s="18" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AH75" s="18" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AI75" s="9"/>
       <c r="AJ75" s="9"/>
@@ -45399,71 +45405,73 @@
     <hyperlink r:id="rId162" ref="AD61"/>
     <hyperlink r:id="rId163" ref="AE61"/>
     <hyperlink r:id="rId164" ref="N63"/>
-    <hyperlink r:id="rId165" ref="AE63"/>
-    <hyperlink r:id="rId166" ref="N65"/>
-    <hyperlink r:id="rId167" ref="O65"/>
-    <hyperlink r:id="rId168" ref="P65"/>
-    <hyperlink r:id="rId169" ref="Q65"/>
-    <hyperlink r:id="rId170" ref="N66"/>
-    <hyperlink r:id="rId171" ref="O66"/>
-    <hyperlink r:id="rId172" ref="P66"/>
-    <hyperlink r:id="rId173" ref="Q66"/>
-    <hyperlink r:id="rId174" ref="AB66"/>
-    <hyperlink r:id="rId175" ref="AC66"/>
-    <hyperlink r:id="rId176" ref="N67"/>
-    <hyperlink r:id="rId177" ref="O67"/>
-    <hyperlink r:id="rId178" ref="P67"/>
-    <hyperlink r:id="rId179" ref="Q67"/>
-    <hyperlink r:id="rId180" ref="M69"/>
-    <hyperlink r:id="rId181" ref="W69"/>
-    <hyperlink r:id="rId182" ref="AB69"/>
-    <hyperlink r:id="rId183" ref="AC69"/>
-    <hyperlink r:id="rId184" ref="AD69"/>
-    <hyperlink r:id="rId185" ref="M70"/>
-    <hyperlink r:id="rId186" ref="W70"/>
-    <hyperlink r:id="rId187" ref="AB70"/>
-    <hyperlink r:id="rId188" ref="AC70"/>
-    <hyperlink r:id="rId189" ref="AD70"/>
-    <hyperlink r:id="rId190" ref="D73"/>
-    <hyperlink r:id="rId191" ref="G73"/>
-    <hyperlink r:id="rId192" ref="M73"/>
-    <hyperlink r:id="rId193" ref="Q73"/>
-    <hyperlink r:id="rId194" ref="R73"/>
-    <hyperlink r:id="rId195" ref="S73"/>
-    <hyperlink r:id="rId196" ref="T73"/>
-    <hyperlink r:id="rId197" ref="U73"/>
-    <hyperlink r:id="rId198" ref="V73"/>
-    <hyperlink r:id="rId199" ref="AB73"/>
-    <hyperlink r:id="rId200" ref="AC73"/>
-    <hyperlink r:id="rId201" ref="AE73"/>
-    <hyperlink r:id="rId202" ref="AG73"/>
-    <hyperlink r:id="rId203" ref="AH73"/>
-    <hyperlink r:id="rId204" ref="D74"/>
-    <hyperlink r:id="rId205" ref="G74"/>
-    <hyperlink r:id="rId206" ref="K74"/>
-    <hyperlink r:id="rId207" ref="M74"/>
-    <hyperlink r:id="rId208" ref="Q74"/>
-    <hyperlink r:id="rId209" ref="R74"/>
-    <hyperlink r:id="rId210" ref="S74"/>
-    <hyperlink r:id="rId211" ref="T74"/>
-    <hyperlink r:id="rId212" ref="U74"/>
-    <hyperlink r:id="rId213" ref="AG74"/>
-    <hyperlink r:id="rId214" ref="AH74"/>
-    <hyperlink r:id="rId215" ref="D75"/>
-    <hyperlink r:id="rId216" ref="G75"/>
-    <hyperlink r:id="rId217" ref="K75"/>
-    <hyperlink r:id="rId218" ref="M75"/>
-    <hyperlink r:id="rId219" ref="Q75"/>
-    <hyperlink r:id="rId220" ref="R75"/>
-    <hyperlink r:id="rId221" ref="S75"/>
-    <hyperlink r:id="rId222" ref="T75"/>
-    <hyperlink r:id="rId223" ref="U75"/>
-    <hyperlink r:id="rId224" ref="AB75"/>
-    <hyperlink r:id="rId225" ref="AC75"/>
-    <hyperlink r:id="rId226" ref="AE75"/>
-    <hyperlink r:id="rId227" ref="AG75"/>
-    <hyperlink r:id="rId228" ref="AH75"/>
+    <hyperlink r:id="rId165" ref="AB63"/>
+    <hyperlink r:id="rId166" ref="AC63"/>
+    <hyperlink r:id="rId167" ref="AE63"/>
+    <hyperlink r:id="rId168" ref="N65"/>
+    <hyperlink r:id="rId169" ref="O65"/>
+    <hyperlink r:id="rId170" ref="P65"/>
+    <hyperlink r:id="rId171" ref="Q65"/>
+    <hyperlink r:id="rId172" ref="N66"/>
+    <hyperlink r:id="rId173" ref="O66"/>
+    <hyperlink r:id="rId174" ref="P66"/>
+    <hyperlink r:id="rId175" ref="Q66"/>
+    <hyperlink r:id="rId176" ref="AB66"/>
+    <hyperlink r:id="rId177" ref="AC66"/>
+    <hyperlink r:id="rId178" ref="N67"/>
+    <hyperlink r:id="rId179" ref="O67"/>
+    <hyperlink r:id="rId180" ref="P67"/>
+    <hyperlink r:id="rId181" ref="Q67"/>
+    <hyperlink r:id="rId182" ref="M69"/>
+    <hyperlink r:id="rId183" ref="W69"/>
+    <hyperlink r:id="rId184" ref="AB69"/>
+    <hyperlink r:id="rId185" ref="AC69"/>
+    <hyperlink r:id="rId186" ref="AD69"/>
+    <hyperlink r:id="rId187" ref="M70"/>
+    <hyperlink r:id="rId188" ref="W70"/>
+    <hyperlink r:id="rId189" ref="AB70"/>
+    <hyperlink r:id="rId190" ref="AC70"/>
+    <hyperlink r:id="rId191" ref="AD70"/>
+    <hyperlink r:id="rId192" ref="D73"/>
+    <hyperlink r:id="rId193" ref="G73"/>
+    <hyperlink r:id="rId194" ref="M73"/>
+    <hyperlink r:id="rId195" ref="Q73"/>
+    <hyperlink r:id="rId196" ref="R73"/>
+    <hyperlink r:id="rId197" ref="S73"/>
+    <hyperlink r:id="rId198" ref="T73"/>
+    <hyperlink r:id="rId199" ref="U73"/>
+    <hyperlink r:id="rId200" ref="V73"/>
+    <hyperlink r:id="rId201" ref="AB73"/>
+    <hyperlink r:id="rId202" ref="AC73"/>
+    <hyperlink r:id="rId203" ref="AE73"/>
+    <hyperlink r:id="rId204" ref="AG73"/>
+    <hyperlink r:id="rId205" ref="AH73"/>
+    <hyperlink r:id="rId206" ref="D74"/>
+    <hyperlink r:id="rId207" ref="G74"/>
+    <hyperlink r:id="rId208" ref="K74"/>
+    <hyperlink r:id="rId209" ref="M74"/>
+    <hyperlink r:id="rId210" ref="Q74"/>
+    <hyperlink r:id="rId211" ref="R74"/>
+    <hyperlink r:id="rId212" ref="S74"/>
+    <hyperlink r:id="rId213" ref="T74"/>
+    <hyperlink r:id="rId214" ref="U74"/>
+    <hyperlink r:id="rId215" ref="AG74"/>
+    <hyperlink r:id="rId216" ref="AH74"/>
+    <hyperlink r:id="rId217" ref="D75"/>
+    <hyperlink r:id="rId218" ref="G75"/>
+    <hyperlink r:id="rId219" ref="K75"/>
+    <hyperlink r:id="rId220" ref="M75"/>
+    <hyperlink r:id="rId221" ref="Q75"/>
+    <hyperlink r:id="rId222" ref="R75"/>
+    <hyperlink r:id="rId223" ref="S75"/>
+    <hyperlink r:id="rId224" ref="T75"/>
+    <hyperlink r:id="rId225" ref="U75"/>
+    <hyperlink r:id="rId226" ref="AB75"/>
+    <hyperlink r:id="rId227" ref="AC75"/>
+    <hyperlink r:id="rId228" ref="AE75"/>
+    <hyperlink r:id="rId229" ref="AG75"/>
+    <hyperlink r:id="rId230" ref="AH75"/>
   </hyperlinks>
-  <drawing r:id="rId229"/>
+  <drawing r:id="rId231"/>
 </worksheet>
 </file>
--- a/lg-com-status-dashboard/신호등-Article.xlsx
+++ b/lg-com-status-dashboard/신호등-Article.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="370">
   <si>
     <t>Title</t>
   </si>
@@ -400,6 +400,9 @@
     <t>How to adjust refrigerator and freezer temperature to keep food fresh and save energy</t>
   </si>
   <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/refrigerators/how-to-adjust-fridge-freezer-temperature/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/tw/appliance-tips-and-guides/refrigerators/how-to-adjust-fridge-freezer-temperature</t>
   </si>
   <si>
@@ -410,6 +413,9 @@
   </si>
   <si>
     <t>Standard refrigerator size: Which one should I choose to meet my needs?</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/refrigerators/standard-refrigerator-size-should-choose/</t>
   </si>
   <si>
     <t>https://www.lg.com/tw/appliance-tips-and-guides/refrigerators/standard-refrigerator-size-should-choose</t>
@@ -424,6 +430,9 @@
     <t>What is a Refrigerator?</t>
   </si>
   <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/refrigerators/what-is-refrigerator-how-keep-food-fresh/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/tw/appliance-tips-and-guides/refrigerators/what-is-refrigerator-how-keep-food-fresh</t>
   </si>
   <si>
@@ -436,6 +445,9 @@
     <t>5tips to organize refrigerator</t>
   </si>
   <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/refrigerators/5-tips-organize-refrigerator/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/tw/appliance-tips-and-guides/refrigerators/5-tips-organize-refrigerator</t>
   </si>
   <si>
@@ -446,6 +458,9 @@
   </si>
   <si>
     <t>How to read electrical label of your refrigerator</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/refrigerators/how-to-read-refrigerator-energy-label/</t>
   </si>
   <si>
     <t>ice solution (TBD)</t>
@@ -694,6 +709,9 @@
     <t>Harmonizing Your Home_fengshui</t>
   </si>
   <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/refrigerators/feung-shui-solutions-for-placing-refrigerators-washing-machine/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/tw/appliance-tips-and-guides/refrigerators/feung-shui-solutions-for-placing-refrigerators-washing-machine/</t>
   </si>
   <si>
@@ -701,6 +719,9 @@
   </si>
   <si>
     <t>How many watts does a washing machine use</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/washer-dryers/how-many-watts-does-a-washing-machine-use/</t>
   </si>
   <si>
     <t>https://www.lg.com/tw/appliance-tips-and-guides/washer-dryers/how-many-watts-does-a-washing-machine-use/</t>
@@ -715,6 +736,9 @@
     <t>How to use washing machines</t>
   </si>
   <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/washer-dryers/how-to-use-an-automatic-washing-machine/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/tw/appliance-tips-and-guides/washer-dryers/how-to-use-an-automatic-washing-machine/</t>
   </si>
   <si>
@@ -725,6 +749,9 @@
   </si>
   <si>
     <t>How to choose a dryer size</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/washer-dryers/how-to-choose-a-right-dryer-size/</t>
   </si>
   <si>
     <t>https://www.lg.com/tw/appliance-tips-and-guides/washer-dryers/how-to-choose-a-right-dryer-size/</t>
@@ -739,6 +766,12 @@
     <t>What temperature should you use to dry a duvet</t>
   </si>
   <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/washer-dryers/what-temperature-dry-duvet/</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/tw/appliance-tips-and-guides/washer-dryers/what-temperature-dry-duvet</t>
+  </si>
+  <si>
     <t>https://www.lg.com/ph/lg-experience/helpful-hints/what-temperature-dry-duvet/</t>
   </si>
   <si>
@@ -746,6 +779,9 @@
   </si>
   <si>
     <t>Washing Machine Temperature Guide</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/washer-dryers/washing-machine-temperature-guide/</t>
   </si>
   <si>
     <t>https://www.lg.com/tw/appliance-tips-and-guides/washer-dryers/washing-machine-temperature-guide/</t>
@@ -760,6 +796,12 @@
     <t>Benefits of having washing machine</t>
   </si>
   <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/washer-dryers/benefits-of-having-washing-machine/</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/tw/appliance-tips-and-guides/washer-dryers/benefits-of-having-washing-machine</t>
+  </si>
+  <si>
     <t>https://www.lg.com/ph/lg-experience/helpful-hints/benefits-of-having-washing-machine/</t>
   </si>
   <si>
@@ -767,6 +809,9 @@
   </si>
   <si>
     <t>How to choose standard washing machine size</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/th/appliance-tips-and-guides/washer-dryers/how-to-choose-standard-washing-machine-size/</t>
   </si>
   <si>
     <t>https://www.lg.com/tw/appliance-tips-and-guides/washer-dryers/how-to-choose-standard-washing-machine-size/</t>
@@ -790,6 +835,9 @@
     <t>https://www.lg.com/vn/lg-experience/goi-y-va-meo/lam-tuong-va-su-that-ve-may-giat-cua-tren/</t>
   </si>
   <si>
+    <t>https://www.lg.com/mx/lg-experience/helpful-hints/mitos-y-verdades-sobre-las-lavadoras-de-carga-superior/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/co/consejos-y-guias-sobre-electrodomesticos/lavadoras/mitos-y-verdades-sobre-las-lavadoras-de-carga-superior/</t>
   </si>
   <si>
@@ -797,9 +845,6 @@
   </si>
   <si>
     <t>https://www.lg.com/ca_fr/experience-lg/conseils-utiles/mythes-et-verites-laveuses-a-chargement-vertical/</t>
-  </si>
-  <si>
-    <t>https://www.lg.com/id/lg-experience/tips/mitos-dan-fakta-mesin-cuci-bukaan-atas/</t>
   </si>
   <si>
     <t>https://www.lg.com/in/magazine/lg-experience-2026-top-load-washing-machine-myths-and-truths/</t>
@@ -843,9 +888,6 @@
   </si>
   <si>
     <t>https://www.lg.com/my/lg-experience/helpful-hints/understanding-vaccum-suction-power/</t>
-  </si>
-  <si>
-    <t>*</t>
   </si>
   <si>
     <t>How to Stop Your Cordless Vacuum From Smelling Bad</t>
@@ -896,7 +938,13 @@
     <t>https://www.lg.com/vn/lg-experience/goi-y-va-meo/cach-ve-sinh-lo-vi-song/</t>
   </si>
   <si>
+    <t>https://www.lg.com/mx/lg-experience/helpful-hints/how-to-clean-a-microwave-without-harsh-chemicals/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/co/consejos-y-guias-sobre-electrodomesticos/coccion/guia-de-tamanos-y-compra-de-microondas/</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/br/lg-experience/dicas-uteis/como-limpar-um-micro-ondas-sem-produtos-quiimicos-agressivos/</t>
   </si>
   <si>
     <t>https://www.lg.com/ca_en/lg-experience/helpful-hints/how-to-clean-a-microwave-without-harsh-chemicals/</t>
@@ -908,13 +956,22 @@
     <t>https://www.lg.com/id/lg-experience/tips/cara-membersihkan-microwave-tanpa-bahan-kimia-keras/</t>
   </si>
   <si>
+    <t>https://www.lg.com/in/magazine/how-to-clean-a-microwave-without-harsh-chemicals/</t>
+  </si>
+  <si>
     <t>MWO buying guide</t>
   </si>
   <si>
     <t>https://www.lg.com/vn/lg-experience/goi-y-va-meo/huong-dan-mua-va-chon-kich-thuoc-lo-vi-song/</t>
   </si>
   <si>
+    <t>https://www.lg.com/mx/lg-experience/helpful-hints/microwave-size-and-buying-guide/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/co/consejos-y-guias-sobre-electrodomesticos/coccion/como-limpiar-un-microondas-sin-sustancias-quimicas-agresivas/</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/br/lg-experience/dicas-uteis/tamanho-do-micro-ondas-e-guia-de-compras/</t>
   </si>
   <si>
     <t>https://www.lg.com/ca_en/lg-experience/helpful-hints/microwave-size-and-buying-guide/</t>
@@ -942,6 +999,9 @@
   </si>
   <si>
     <t>https://www.lg.com/it/quanta-acqua-ed-energia-consuma-una-lavastoviglie/</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/tw/appliance-tips-and-guides/dishwashers/how-much-water-and-energy-does-a-dishwasher-use/</t>
   </si>
   <si>
     <t>https://www.lg.com/vn/lg-experience/goi-y-va-meo/may-rua-bat-tieu-thu-bao-nhieu-dien-va-nuoc/</t>
@@ -989,7 +1049,7 @@
     <t>https://www.lg.com/it/lavastoviglie-da-incasso-vs-lavastoviglie-a-libera-installazione/</t>
   </si>
   <si>
-    <t>https://www.lg.com/tw/appliance-tips-and-guides/integrated-dishwashers-vs-freestanding-dishwashers/</t>
+    <t>https://www.lg.com/tw/appliance-tips-and-guides/dishwashers/integrated-dishwashers-vs-freestanding-dishwashers/</t>
   </si>
   <si>
     <t>https://www.lg.com/vn/lg-experience/may-rua-bat-am-tu-vs-may-rua-bat-doc-lap/</t>
@@ -1010,6 +1070,9 @@
     <t>https://www.lg.com/eg_en/appliance-tips-and-guides/dishwasher/integrated-dishwashers-vs-freestanding-dishwashers/</t>
   </si>
   <si>
+    <t>https://www.lg.com/mx/lg-experience/helpful-hints/integrated-dishwashers-vs-freestanding-dishwashers/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/ae/appliances/tips-and-guides/integrated-dishwashers-vs-freestanding-dishwashers</t>
   </si>
   <si>
@@ -1025,7 +1088,7 @@
     <t>https://www.lg.com/it/magazine/the-ultimate-guide-to-dishwasher-maintenance/</t>
   </si>
   <si>
-    <t>https://www.lg.com/tw/appliance-tips-and-guides/the-ultimate-guide-to-dishwasher-maintenance/</t>
+    <t>https://www.lg.com/tw/appliance-tips-and-guides/dishwashers/the-ultimate-guide-to-dishwasher-maintenance/</t>
   </si>
   <si>
     <t>https://www.lg.com/vn/lg-experience/huong-dan-bao-tri-may-rua-bat/</t>
@@ -1069,7 +1132,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm월 dd일"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="43">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1200,6 +1263,11 @@
     </font>
     <font>
       <u/>
+      <color rgb="FF000000"/>
+      <name val="Dotum"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
@@ -1267,6 +1335,11 @@
     <font>
       <color rgb="FF000000"/>
       <name val="&quot;Microsoft GothicNeo&quot;"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -1443,46 +1516,46 @@
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1497,25 +1570,25 @@
     <xf borderId="2" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1524,13 +1597,13 @@
     <xf borderId="3" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1539,16 +1612,16 @@
     <xf borderId="6" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1557,157 +1630,157 @@
     <xf borderId="6" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="3" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="10" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="11" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="3" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="13" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="11" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="11" fillId="3" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="3" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="14" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="11" fillId="3" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="3" fontId="36" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="36" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="37" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="37" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="38" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="39" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="13" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="38" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="40" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1716,17 +1789,17 @@
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="38" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="40" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="39" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="40" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="41" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="42" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2243,7 +2316,7 @@
         <v>55</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H5" s="22" t="s">
         <v>55</v>
@@ -2304,7 +2377,7 @@
         <v>59</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I6" s="21" t="s">
         <v>56</v>
@@ -2478,7 +2551,7 @@
         <v>68</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I9" s="21" t="s">
         <v>56</v>
@@ -3366,16 +3439,16 @@
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
       <c r="J25" s="44" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="K25" s="45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L25" s="46" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M25" s="47" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N25" s="48" t="s">
         <v>54</v>
@@ -3413,7 +3486,7 @@
         <v>51</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
@@ -3422,16 +3495,16 @@
       <c r="H26" s="35"/>
       <c r="I26" s="35"/>
       <c r="J26" s="44" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="K26" s="45" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L26" s="46" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M26" s="47" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N26" s="48" t="s">
         <v>54</v>
@@ -3469,7 +3542,7 @@
         <v>51</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
@@ -3478,16 +3551,16 @@
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
       <c r="J27" s="44" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="K27" s="45" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L27" s="47" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M27" s="47" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="N27" s="48" t="s">
         <v>54</v>
@@ -3525,7 +3598,7 @@
         <v>51</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D28" s="25"/>
       <c r="E28" s="25"/>
@@ -3534,16 +3607,16 @@
       <c r="H28" s="25"/>
       <c r="I28" s="25"/>
       <c r="J28" s="44" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="K28" s="45" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L28" s="46" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="M28" s="47" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N28" s="48" t="s">
         <v>54</v>
@@ -3581,7 +3654,7 @@
         <v>51</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="25"/>
@@ -3590,7 +3663,7 @@
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="J29" s="44" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="K29" s="13"/>
       <c r="L29" s="14"/>
@@ -3631,7 +3704,7 @@
         <v>51</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="25"/>
@@ -3677,7 +3750,7 @@
         <v>51</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="25"/>
@@ -3720,16 +3793,16 @@
     <row r="32">
       <c r="A32" s="10"/>
       <c r="B32" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D32" s="54" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F32" s="22" t="s">
         <v>55</v>
@@ -3778,16 +3851,16 @@
     <row r="33">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D33" s="54" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F33" s="22" t="s">
         <v>55</v>
@@ -3836,16 +3909,16 @@
     <row r="34">
       <c r="A34" s="10"/>
       <c r="B34" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E34" s="38" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F34" s="22" t="s">
         <v>55</v>
@@ -3894,16 +3967,16 @@
     <row r="35">
       <c r="A35" s="10"/>
       <c r="B35" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D35" s="54" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E35" s="38" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F35" s="22" t="s">
         <v>55</v>
@@ -3952,16 +4025,16 @@
     <row r="36">
       <c r="A36" s="10"/>
       <c r="B36" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E36" s="38" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F36" s="22" t="s">
         <v>55</v>
@@ -4010,13 +4083,13 @@
     <row r="37">
       <c r="A37" s="10"/>
       <c r="B37" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D37" s="54" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E37" s="30" t="s">
         <v>54</v>
@@ -4025,10 +4098,10 @@
         <v>55</v>
       </c>
       <c r="G37" s="31" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I37" s="21" t="s">
         <v>56</v>
@@ -4068,13 +4141,13 @@
     <row r="38">
       <c r="A38" s="10"/>
       <c r="B38" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D38" s="54" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E38" s="30" t="s">
         <v>54</v>
@@ -4083,7 +4156,7 @@
         <v>55</v>
       </c>
       <c r="G38" s="31" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="H38" s="22" t="s">
         <v>55</v>
@@ -4128,13 +4201,13 @@
     <row r="39">
       <c r="A39" s="10"/>
       <c r="B39" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D39" s="54" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E39" s="30" t="s">
         <v>54</v>
@@ -4143,7 +4216,7 @@
         <v>55</v>
       </c>
       <c r="G39" s="31" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H39" s="22" t="s">
         <v>55</v>
@@ -4188,13 +4261,13 @@
     <row r="40">
       <c r="A40" s="10"/>
       <c r="B40" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D40" s="54" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E40" s="30" t="s">
         <v>54</v>
@@ -4203,7 +4276,7 @@
         <v>55</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H40" s="22" t="s">
         <v>55</v>
@@ -4246,13 +4319,13 @@
     <row r="41">
       <c r="A41" s="10"/>
       <c r="B41" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D41" s="54" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E41" s="30" t="s">
         <v>54</v>
@@ -4261,10 +4334,10 @@
         <v>55</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I41" s="21" t="s">
         <v>56</v>
@@ -4306,13 +4379,13 @@
     <row r="42">
       <c r="A42" s="10"/>
       <c r="B42" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D42" s="54" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E42" s="22" t="s">
         <v>55</v>
@@ -4321,7 +4394,7 @@
         <v>55</v>
       </c>
       <c r="G42" s="31" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H42" s="22" t="s">
         <v>55</v>
@@ -4364,10 +4437,10 @@
     <row r="43">
       <c r="A43" s="10"/>
       <c r="B43" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D43" s="25"/>
       <c r="E43" s="25"/>
@@ -4384,16 +4457,16 @@
       <c r="P43" s="16"/>
       <c r="Q43" s="23"/>
       <c r="R43" s="38" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="S43" s="33" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="T43" s="33" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="U43" s="38" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="V43" s="25"/>
       <c r="W43" s="25"/>
@@ -4418,10 +4491,10 @@
     <row r="44">
       <c r="A44" s="10"/>
       <c r="B44" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D44" s="25"/>
       <c r="E44" s="25"/>
@@ -4438,16 +4511,16 @@
       <c r="P44" s="16"/>
       <c r="Q44" s="23"/>
       <c r="R44" s="38" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="S44" s="33" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="T44" s="33" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="U44" s="38" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="V44" s="25"/>
       <c r="W44" s="25"/>
@@ -4472,10 +4545,10 @@
     <row r="45">
       <c r="A45" s="10"/>
       <c r="B45" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D45" s="25"/>
       <c r="E45" s="25"/>
@@ -4492,16 +4565,16 @@
       <c r="P45" s="16"/>
       <c r="Q45" s="23"/>
       <c r="R45" s="38" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="S45" s="33" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="T45" s="33" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="U45" s="38" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="V45" s="25"/>
       <c r="W45" s="25"/>
@@ -4526,10 +4599,10 @@
     <row r="46">
       <c r="A46" s="10"/>
       <c r="B46" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D46" s="25"/>
       <c r="E46" s="25"/>
@@ -4550,16 +4623,16 @@
       <c r="T46" s="25"/>
       <c r="U46" s="25"/>
       <c r="V46" s="38" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="W46" s="33" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="X46" s="38" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="Y46" s="38" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Z46" s="59" t="s">
         <v>55</v>
@@ -4582,10 +4655,10 @@
     <row r="47">
       <c r="A47" s="10"/>
       <c r="B47" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D47" s="35"/>
       <c r="E47" s="25"/>
@@ -4606,16 +4679,16 @@
       <c r="T47" s="25"/>
       <c r="U47" s="25"/>
       <c r="V47" s="38" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="W47" s="60" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="X47" s="38" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Y47" s="38" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Z47" s="22" t="s">
         <v>55</v>
@@ -4638,10 +4711,10 @@
     <row r="48">
       <c r="A48" s="10"/>
       <c r="B48" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D48" s="23"/>
       <c r="E48" s="25"/>
@@ -4662,16 +4735,16 @@
       <c r="T48" s="25"/>
       <c r="U48" s="25"/>
       <c r="V48" s="38" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="W48" s="60" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="X48" s="38" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="Y48" s="38" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="Z48" s="22" t="s">
         <v>55</v>
@@ -4694,10 +4767,10 @@
     <row r="49">
       <c r="A49" s="10"/>
       <c r="B49" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D49" s="25"/>
       <c r="E49" s="25"/>
@@ -4718,16 +4791,16 @@
       <c r="T49" s="25"/>
       <c r="U49" s="25"/>
       <c r="V49" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="W49" s="60" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="X49" s="38" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Y49" s="38" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="Z49" s="22" t="s">
         <v>55</v>
@@ -4750,10 +4823,10 @@
     <row r="50">
       <c r="A50" s="10"/>
       <c r="B50" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D50" s="25"/>
       <c r="E50" s="25"/>
@@ -4774,16 +4847,16 @@
       <c r="T50" s="25"/>
       <c r="U50" s="25"/>
       <c r="V50" s="38" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="W50" s="60" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="X50" s="38" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Y50" s="38" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Z50" s="22" t="s">
         <v>55</v>
@@ -4806,10 +4879,10 @@
     <row r="51">
       <c r="A51" s="10"/>
       <c r="B51" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D51" s="25"/>
       <c r="E51" s="35"/>
@@ -4830,16 +4903,16 @@
       <c r="T51" s="35"/>
       <c r="U51" s="35"/>
       <c r="V51" s="64" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="W51" s="65" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="X51" s="66" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Y51" s="66" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Z51" s="67" t="s">
         <v>55</v>
@@ -4862,10 +4935,10 @@
     <row r="52">
       <c r="A52" s="10"/>
       <c r="B52" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D52" s="26"/>
       <c r="E52" s="16"/>
@@ -4873,15 +4946,15 @@
       <c r="G52" s="16"/>
       <c r="H52" s="16"/>
       <c r="I52" s="16"/>
-      <c r="J52" s="13" t="s">
-        <v>55</v>
+      <c r="J52" s="45" t="s">
+        <v>232</v>
       </c>
       <c r="K52" s="45" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L52" s="14"/>
       <c r="M52" s="45" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="N52" s="14" t="s">
         <v>54</v>
@@ -4916,10 +4989,10 @@
     <row r="53">
       <c r="A53" s="10"/>
       <c r="B53" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D53" s="26"/>
       <c r="E53" s="16"/>
@@ -4927,17 +5000,17 @@
       <c r="G53" s="16"/>
       <c r="H53" s="16"/>
       <c r="I53" s="16"/>
-      <c r="J53" s="13" t="s">
-        <v>55</v>
+      <c r="J53" s="45" t="s">
+        <v>236</v>
       </c>
       <c r="K53" s="47" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="L53" s="69" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M53" s="47" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="N53" s="14" t="s">
         <v>54</v>
@@ -4972,10 +5045,10 @@
     <row r="54">
       <c r="A54" s="10"/>
       <c r="B54" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="D54" s="26"/>
       <c r="E54" s="16"/>
@@ -4983,17 +5056,17 @@
       <c r="G54" s="16"/>
       <c r="H54" s="16"/>
       <c r="I54" s="16"/>
-      <c r="J54" s="13" t="s">
-        <v>55</v>
+      <c r="J54" s="45" t="s">
+        <v>241</v>
       </c>
       <c r="K54" s="47" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="L54" s="69" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="M54" s="47" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="N54" s="14" t="s">
         <v>54</v>
@@ -5028,10 +5101,10 @@
     <row r="55">
       <c r="A55" s="10"/>
       <c r="B55" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D55" s="26"/>
       <c r="E55" s="16"/>
@@ -5039,17 +5112,17 @@
       <c r="G55" s="16"/>
       <c r="H55" s="16"/>
       <c r="I55" s="16"/>
-      <c r="J55" s="13" t="s">
-        <v>55</v>
+      <c r="J55" s="45" t="s">
+        <v>246</v>
       </c>
       <c r="K55" s="47" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="L55" s="69" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="M55" s="47" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="N55" s="14" t="s">
         <v>54</v>
@@ -5084,10 +5157,10 @@
     <row r="56">
       <c r="A56" s="10"/>
       <c r="B56" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D56" s="26"/>
       <c r="E56" s="16"/>
@@ -5095,17 +5168,17 @@
       <c r="G56" s="16"/>
       <c r="H56" s="16"/>
       <c r="I56" s="16"/>
-      <c r="J56" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="K56" s="13" t="s">
-        <v>55</v>
+      <c r="J56" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="K56" s="45" t="s">
+        <v>252</v>
       </c>
       <c r="L56" s="47" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="M56" s="47" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="N56" s="14" t="s">
         <v>54</v>
@@ -5140,10 +5213,10 @@
     <row r="57">
       <c r="A57" s="10"/>
       <c r="B57" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D57" s="26"/>
       <c r="E57" s="16"/>
@@ -5151,17 +5224,17 @@
       <c r="G57" s="16"/>
       <c r="H57" s="16"/>
       <c r="I57" s="16"/>
-      <c r="J57" s="13" t="s">
-        <v>55</v>
+      <c r="J57" s="45" t="s">
+        <v>256</v>
       </c>
       <c r="K57" s="47" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="L57" s="69" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="M57" s="47" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="N57" s="14" t="s">
         <v>54</v>
@@ -5196,10 +5269,10 @@
     <row r="58">
       <c r="A58" s="10"/>
       <c r="B58" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D58" s="26"/>
       <c r="E58" s="16"/>
@@ -5207,17 +5280,17 @@
       <c r="G58" s="16"/>
       <c r="H58" s="16"/>
       <c r="I58" s="16"/>
-      <c r="J58" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="K58" s="13" t="s">
-        <v>55</v>
+      <c r="J58" s="45" t="s">
+        <v>261</v>
+      </c>
+      <c r="K58" s="45" t="s">
+        <v>262</v>
       </c>
       <c r="L58" s="69" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="M58" s="47" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="N58" s="14" t="s">
         <v>54</v>
@@ -5252,10 +5325,10 @@
     <row r="59">
       <c r="A59" s="10"/>
       <c r="B59" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="D59" s="36"/>
       <c r="E59" s="16"/>
@@ -5263,17 +5336,17 @@
       <c r="G59" s="16"/>
       <c r="H59" s="16"/>
       <c r="I59" s="16"/>
-      <c r="J59" s="13" t="s">
-        <v>55</v>
+      <c r="J59" s="45" t="s">
+        <v>266</v>
       </c>
       <c r="K59" s="47" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="L59" s="46" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="M59" s="47" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="N59" s="14" t="s">
         <v>54</v>
@@ -5308,14 +5381,14 @@
     <row r="60">
       <c r="A60" s="10"/>
       <c r="B60" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D60" s="70"/>
       <c r="E60" s="47" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="F60" s="16"/>
       <c r="G60" s="16"/>
@@ -5356,14 +5429,12 @@
     <row r="61">
       <c r="A61" s="10"/>
       <c r="B61" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>54</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="D61" s="14"/>
       <c r="E61" s="14" t="s">
         <v>54</v>
       </c>
@@ -5383,7 +5454,7 @@
       </c>
       <c r="L61" s="16"/>
       <c r="M61" s="45" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="N61" s="14" t="s">
         <v>54</v>
@@ -5399,29 +5470,29 @@
       </c>
       <c r="T61" s="16"/>
       <c r="U61" s="16"/>
-      <c r="V61" s="14" t="s">
-        <v>54</v>
+      <c r="V61" s="12" t="s">
+        <v>274</v>
       </c>
       <c r="W61" s="71" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="X61" s="16"/>
       <c r="Y61" s="16"/>
       <c r="Z61" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA61" s="16"/>
       <c r="AB61" s="47" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="AC61" s="47" t="s">
-        <v>261</v>
-      </c>
-      <c r="AD61" s="12" t="s">
-        <v>262</v>
+        <v>277</v>
+      </c>
+      <c r="AD61" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="AE61" s="12" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="AF61" s="14" t="s">
         <v>56</v>
@@ -5438,10 +5509,10 @@
     <row r="62">
       <c r="A62" s="10"/>
       <c r="B62" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
@@ -5484,10 +5555,10 @@
     <row r="63">
       <c r="A63" s="10"/>
       <c r="B63" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D63" s="72" t="s">
         <v>54</v>
@@ -5514,16 +5585,16 @@
         <v>56</v>
       </c>
       <c r="N63" s="73" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="O63" s="62"/>
       <c r="P63" s="62"/>
       <c r="Q63" s="62"/>
       <c r="R63" s="72" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S63" s="72" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T63" s="62"/>
       <c r="U63" s="62"/>
@@ -5540,16 +5611,16 @@
       </c>
       <c r="AA63" s="62"/>
       <c r="AB63" s="12" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="AC63" s="12" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="AD63" s="72" t="s">
         <v>54</v>
       </c>
       <c r="AE63" s="75" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="AF63" s="62"/>
       <c r="AG63" s="76"/>
@@ -5564,10 +5635,10 @@
     <row r="64">
       <c r="A64" s="10"/>
       <c r="B64" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
@@ -5616,10 +5687,10 @@
     <row r="65">
       <c r="A65" s="10"/>
       <c r="B65" s="10" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D65" s="16"/>
       <c r="E65" s="52"/>
@@ -5636,20 +5707,18 @@
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
       <c r="N65" s="12" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="O65" s="12" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="P65" s="12" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="R65" s="10" t="s">
-        <v>277</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="R65" s="10"/>
       <c r="S65" s="16"/>
       <c r="T65" s="16"/>
       <c r="U65" s="16"/>
@@ -5676,10 +5745,10 @@
     <row r="66">
       <c r="A66" s="10"/>
       <c r="B66" s="10" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
@@ -5696,20 +5765,18 @@
       <c r="L66" s="9"/>
       <c r="M66" s="77"/>
       <c r="N66" s="18" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="O66" s="18" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="P66" s="18" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="Q66" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="R66" s="17" t="s">
-        <v>277</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="R66" s="17"/>
       <c r="S66" s="9"/>
       <c r="T66" s="9"/>
       <c r="U66" s="9"/>
@@ -5720,14 +5787,12 @@
       <c r="Z66" s="9"/>
       <c r="AA66" s="9"/>
       <c r="AB66" s="18" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="AC66" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="AD66" s="17" t="s">
-        <v>277</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="AD66" s="17"/>
       <c r="AE66" s="9"/>
       <c r="AF66" s="9"/>
       <c r="AG66" s="9"/>
@@ -5742,10 +5807,10 @@
     <row r="67">
       <c r="A67" s="10"/>
       <c r="B67" s="10" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
@@ -5762,20 +5827,18 @@
       <c r="L67" s="16"/>
       <c r="M67" s="79"/>
       <c r="N67" s="12" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="O67" s="12" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="P67" s="12" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="R67" s="14" t="s">
-        <v>277</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="R67" s="14"/>
       <c r="S67" s="14"/>
       <c r="T67" s="16"/>
       <c r="U67" s="16"/>
@@ -5802,10 +5865,10 @@
     <row r="68">
       <c r="A68" s="10"/>
       <c r="B68" s="10" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
@@ -5860,78 +5923,74 @@
     <row r="69">
       <c r="A69" s="10"/>
       <c r="B69" s="82" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C69" s="82" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F69" s="83" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I69" s="16"/>
       <c r="J69" s="16"/>
       <c r="K69" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L69" s="16"/>
       <c r="M69" s="15" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O69" s="16"/>
       <c r="P69" s="16"/>
       <c r="Q69" s="16"/>
       <c r="R69" s="84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S69" s="84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T69" s="16"/>
       <c r="U69" s="16"/>
-      <c r="V69" s="10" t="s">
-        <v>56</v>
+      <c r="V69" s="15" t="s">
+        <v>308</v>
       </c>
       <c r="W69" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="X69" s="10" t="s">
-        <v>277</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="X69" s="10"/>
       <c r="Y69" s="16"/>
       <c r="Z69" s="85" t="s">
-        <v>56</v>
+        <v>310</v>
       </c>
       <c r="AA69" s="16"/>
       <c r="AB69" s="15" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="AC69" s="15" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="AD69" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="AE69" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF69" s="10" t="s">
-        <v>56</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="AE69" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="AF69" s="10"/>
       <c r="AG69" s="9"/>
       <c r="AH69" s="9"/>
       <c r="AI69" s="9"/>
@@ -5944,78 +6003,74 @@
     <row r="70">
       <c r="A70" s="10"/>
       <c r="B70" s="82" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C70" s="82" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="D70" s="86" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E70" s="87" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I70" s="16"/>
       <c r="J70" s="16"/>
       <c r="K70" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L70" s="16"/>
       <c r="M70" s="15" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O70" s="16"/>
       <c r="P70" s="16"/>
       <c r="Q70" s="16"/>
       <c r="R70" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T70" s="16"/>
       <c r="U70" s="16"/>
-      <c r="V70" s="10" t="s">
-        <v>56</v>
+      <c r="V70" s="15" t="s">
+        <v>317</v>
       </c>
       <c r="W70" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="X70" s="10" t="s">
-        <v>277</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="X70" s="10"/>
       <c r="Y70" s="16"/>
-      <c r="Z70" s="10" t="s">
-        <v>56</v>
+      <c r="Z70" s="15" t="s">
+        <v>319</v>
       </c>
       <c r="AA70" s="27"/>
       <c r="AB70" s="15" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="AC70" s="15" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="AD70" s="15" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="AE70" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF70" s="10" t="s">
-        <v>56</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="AF70" s="10"/>
       <c r="AG70" s="9"/>
       <c r="AH70" s="9"/>
       <c r="AI70" s="9"/>
@@ -6028,10 +6083,10 @@
     <row r="71">
       <c r="A71" s="10"/>
       <c r="B71" s="82" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C71" s="82" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="D71" s="88"/>
       <c r="E71" s="14"/>
@@ -6074,10 +6129,10 @@
     <row r="72">
       <c r="A72" s="10"/>
       <c r="B72" s="82" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C72" s="82" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="D72" s="93"/>
       <c r="E72" s="14"/>
@@ -6120,13 +6175,13 @@
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="82" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C73" s="82" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="D73" s="95" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>54</v>
@@ -6135,7 +6190,7 @@
         <v>54</v>
       </c>
       <c r="G73" s="47" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="H73" s="14" t="s">
         <v>55</v>
@@ -6144,12 +6199,12 @@
       <c r="J73" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="K73" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="L73" s="92"/>
+      <c r="K73" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="L73" s="96"/>
       <c r="M73" s="12" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="N73" s="14" t="s">
         <v>54</v>
@@ -6157,50 +6212,48 @@
       <c r="O73" s="49"/>
       <c r="P73" s="49"/>
       <c r="Q73" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="R73" s="96" t="s">
-        <v>312</v>
-      </c>
-      <c r="S73" s="96" t="s">
-        <v>313</v>
+        <v>331</v>
+      </c>
+      <c r="R73" s="97" t="s">
+        <v>332</v>
+      </c>
+      <c r="S73" s="97" t="s">
+        <v>333</v>
       </c>
       <c r="T73" s="47" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="U73" s="47" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="V73" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="W73" s="14" t="s">
-        <v>56</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="W73" s="14"/>
       <c r="X73" s="92"/>
-      <c r="Y73" s="14"/>
+      <c r="Y73" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="Z73" s="92"/>
       <c r="AA73" s="89"/>
       <c r="AB73" s="47" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="AC73" s="47" t="s">
-        <v>318</v>
-      </c>
-      <c r="AD73" s="97" t="s">
-        <v>277</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="AD73" s="96"/>
       <c r="AE73" s="12" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="AF73" s="14" t="s">
         <v>56</v>
       </c>
       <c r="AG73" s="18" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AH73" s="18" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="AI73" s="9"/>
       <c r="AJ73" s="9"/>
@@ -6212,13 +6265,13 @@
     <row r="74">
       <c r="A74" s="9"/>
       <c r="B74" s="17" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="E74" s="17" t="s">
         <v>54</v>
@@ -6227,7 +6280,7 @@
         <v>54</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>54</v>
@@ -6237,11 +6290,11 @@
         <v>54</v>
       </c>
       <c r="K74" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="L74" s="9"/>
+        <v>345</v>
+      </c>
+      <c r="L74" s="17"/>
       <c r="M74" s="18" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="N74" s="17" t="s">
         <v>54</v>
@@ -6249,22 +6302,22 @@
       <c r="O74" s="9"/>
       <c r="P74" s="9"/>
       <c r="Q74" s="18" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="R74" s="18" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="S74" s="18" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="T74" s="18" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="U74" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="V74" s="17" t="s">
-        <v>56</v>
+        <v>351</v>
+      </c>
+      <c r="V74" s="18" t="s">
+        <v>352</v>
       </c>
       <c r="W74" s="17" t="s">
         <v>56</v>
@@ -6283,10 +6336,10 @@
         <v>56</v>
       </c>
       <c r="AG74" s="18" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="AH74" s="18" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="AI74" s="9"/>
       <c r="AJ74" s="9"/>
@@ -6298,13 +6351,13 @@
     <row r="75" ht="18.0" customHeight="1">
       <c r="A75" s="9"/>
       <c r="B75" s="17" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>54</v>
@@ -6313,7 +6366,7 @@
         <v>54</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>54</v>
@@ -6323,11 +6376,11 @@
         <v>54</v>
       </c>
       <c r="K75" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="L75" s="9"/>
+        <v>358</v>
+      </c>
+      <c r="L75" s="17"/>
       <c r="M75" s="18" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="N75" s="17" t="s">
         <v>54</v>
@@ -6335,22 +6388,22 @@
       <c r="O75" s="9"/>
       <c r="P75" s="9"/>
       <c r="Q75" s="18" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="R75" s="18" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="S75" s="18" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="T75" s="18" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="U75" s="18" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="V75" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="W75" s="17" t="s">
         <v>56</v>
@@ -6362,25 +6415,23 @@
       <c r="Z75" s="9"/>
       <c r="AA75" s="9"/>
       <c r="AB75" s="18" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="AC75" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="AD75" s="17" t="s">
-        <v>277</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="AD75" s="17"/>
       <c r="AE75" s="18" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="AF75" s="17" t="s">
         <v>56</v>
       </c>
       <c r="AG75" s="18" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="AH75" s="18" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="AI75" s="9"/>
       <c r="AJ75" s="9"/>
@@ -45306,172 +45357,194 @@
     <hyperlink r:id="rId63" ref="W22"/>
     <hyperlink r:id="rId64" ref="X22"/>
     <hyperlink r:id="rId65" ref="Y22"/>
-    <hyperlink r:id="rId66" ref="K25"/>
-    <hyperlink r:id="rId67" ref="L25"/>
-    <hyperlink r:id="rId68" ref="M25"/>
-    <hyperlink r:id="rId69" ref="K26"/>
-    <hyperlink r:id="rId70" ref="L26"/>
-    <hyperlink r:id="rId71" ref="M26"/>
-    <hyperlink r:id="rId72" ref="K27"/>
-    <hyperlink r:id="rId73" ref="L27"/>
-    <hyperlink r:id="rId74" ref="M27"/>
-    <hyperlink r:id="rId75" ref="K28"/>
-    <hyperlink r:id="rId76" ref="L28"/>
-    <hyperlink r:id="rId77" ref="M28"/>
-    <hyperlink r:id="rId78" ref="D32"/>
-    <hyperlink r:id="rId79" ref="E32"/>
-    <hyperlink r:id="rId80" ref="D33"/>
-    <hyperlink r:id="rId81" ref="E33"/>
-    <hyperlink r:id="rId82" ref="D34"/>
-    <hyperlink r:id="rId83" ref="E34"/>
-    <hyperlink r:id="rId84" ref="D35"/>
-    <hyperlink r:id="rId85" ref="E35"/>
-    <hyperlink r:id="rId86" ref="D36"/>
-    <hyperlink r:id="rId87" ref="E36"/>
-    <hyperlink r:id="rId88" ref="D37"/>
-    <hyperlink r:id="rId89" ref="G37"/>
-    <hyperlink r:id="rId90" ref="D38"/>
-    <hyperlink r:id="rId91" ref="G38"/>
-    <hyperlink r:id="rId92" ref="D39"/>
-    <hyperlink r:id="rId93" ref="G39"/>
-    <hyperlink r:id="rId94" ref="D40"/>
-    <hyperlink r:id="rId95" ref="G40"/>
-    <hyperlink r:id="rId96" ref="D41"/>
-    <hyperlink r:id="rId97" ref="G41"/>
-    <hyperlink r:id="rId98" ref="D42"/>
-    <hyperlink r:id="rId99" ref="G42"/>
-    <hyperlink r:id="rId100" ref="R43"/>
-    <hyperlink r:id="rId101" ref="S43"/>
-    <hyperlink r:id="rId102" ref="T43"/>
-    <hyperlink r:id="rId103" ref="U43"/>
-    <hyperlink r:id="rId104" ref="R44"/>
-    <hyperlink r:id="rId105" ref="S44"/>
-    <hyperlink r:id="rId106" ref="T44"/>
-    <hyperlink r:id="rId107" ref="U44"/>
-    <hyperlink r:id="rId108" ref="R45"/>
-    <hyperlink r:id="rId109" ref="S45"/>
-    <hyperlink r:id="rId110" ref="T45"/>
-    <hyperlink r:id="rId111" ref="U45"/>
-    <hyperlink r:id="rId112" ref="V46"/>
-    <hyperlink r:id="rId113" ref="W46"/>
-    <hyperlink r:id="rId114" ref="X46"/>
-    <hyperlink r:id="rId115" ref="Y46"/>
-    <hyperlink r:id="rId116" ref="V47"/>
-    <hyperlink r:id="rId117" ref="W47"/>
-    <hyperlink r:id="rId118" ref="X47"/>
-    <hyperlink r:id="rId119" ref="Y47"/>
-    <hyperlink r:id="rId120" ref="V48"/>
-    <hyperlink r:id="rId121" ref="W48"/>
-    <hyperlink r:id="rId122" ref="X48"/>
-    <hyperlink r:id="rId123" ref="Y48"/>
-    <hyperlink r:id="rId124" ref="V49"/>
-    <hyperlink r:id="rId125" ref="W49"/>
-    <hyperlink r:id="rId126" ref="X49"/>
-    <hyperlink r:id="rId127" ref="Y49"/>
-    <hyperlink r:id="rId128" ref="V50"/>
-    <hyperlink r:id="rId129" ref="W50"/>
-    <hyperlink r:id="rId130" ref="X50"/>
-    <hyperlink r:id="rId131" ref="Y50"/>
-    <hyperlink r:id="rId132" ref="V51"/>
-    <hyperlink r:id="rId133" ref="W51"/>
-    <hyperlink r:id="rId134" ref="X51"/>
-    <hyperlink r:id="rId135" ref="Y51"/>
-    <hyperlink r:id="rId136" ref="K52"/>
-    <hyperlink r:id="rId137" ref="M52"/>
-    <hyperlink r:id="rId138" ref="K53"/>
-    <hyperlink r:id="rId139" ref="L53"/>
-    <hyperlink r:id="rId140" ref="M53"/>
-    <hyperlink r:id="rId141" ref="K54"/>
-    <hyperlink r:id="rId142" ref="L54"/>
-    <hyperlink r:id="rId143" ref="M54"/>
-    <hyperlink r:id="rId144" ref="K55"/>
-    <hyperlink r:id="rId145" ref="L55"/>
-    <hyperlink r:id="rId146" ref="M55"/>
-    <hyperlink r:id="rId147" ref="L56"/>
-    <hyperlink r:id="rId148" ref="M56"/>
-    <hyperlink r:id="rId149" ref="K57"/>
-    <hyperlink r:id="rId150" ref="L57"/>
-    <hyperlink r:id="rId151" ref="M57"/>
-    <hyperlink r:id="rId152" ref="L58"/>
-    <hyperlink r:id="rId153" ref="M58"/>
-    <hyperlink r:id="rId154" ref="K59"/>
-    <hyperlink r:id="rId155" ref="L59"/>
-    <hyperlink r:id="rId156" ref="M59"/>
-    <hyperlink r:id="rId157" ref="E60"/>
-    <hyperlink r:id="rId158" ref="M61"/>
-    <hyperlink r:id="rId159" ref="W61"/>
-    <hyperlink r:id="rId160" ref="AB61"/>
-    <hyperlink r:id="rId161" ref="AC61"/>
-    <hyperlink r:id="rId162" ref="AD61"/>
-    <hyperlink r:id="rId163" ref="AE61"/>
-    <hyperlink r:id="rId164" ref="N63"/>
-    <hyperlink r:id="rId165" ref="AB63"/>
-    <hyperlink r:id="rId166" ref="AC63"/>
-    <hyperlink r:id="rId167" ref="AE63"/>
-    <hyperlink r:id="rId168" ref="N65"/>
-    <hyperlink r:id="rId169" ref="O65"/>
-    <hyperlink r:id="rId170" ref="P65"/>
-    <hyperlink r:id="rId171" ref="Q65"/>
-    <hyperlink r:id="rId172" ref="N66"/>
-    <hyperlink r:id="rId173" ref="O66"/>
-    <hyperlink r:id="rId174" ref="P66"/>
-    <hyperlink r:id="rId175" ref="Q66"/>
-    <hyperlink r:id="rId176" ref="AB66"/>
-    <hyperlink r:id="rId177" ref="AC66"/>
-    <hyperlink r:id="rId178" ref="N67"/>
-    <hyperlink r:id="rId179" ref="O67"/>
-    <hyperlink r:id="rId180" ref="P67"/>
-    <hyperlink r:id="rId181" ref="Q67"/>
-    <hyperlink r:id="rId182" ref="M69"/>
-    <hyperlink r:id="rId183" ref="W69"/>
-    <hyperlink r:id="rId184" ref="AB69"/>
-    <hyperlink r:id="rId185" ref="AC69"/>
-    <hyperlink r:id="rId186" ref="AD69"/>
-    <hyperlink r:id="rId187" ref="M70"/>
-    <hyperlink r:id="rId188" ref="W70"/>
-    <hyperlink r:id="rId189" ref="AB70"/>
-    <hyperlink r:id="rId190" ref="AC70"/>
-    <hyperlink r:id="rId191" ref="AD70"/>
-    <hyperlink r:id="rId192" ref="D73"/>
-    <hyperlink r:id="rId193" ref="G73"/>
-    <hyperlink r:id="rId194" ref="M73"/>
-    <hyperlink r:id="rId195" ref="Q73"/>
-    <hyperlink r:id="rId196" ref="R73"/>
-    <hyperlink r:id="rId197" ref="S73"/>
-    <hyperlink r:id="rId198" ref="T73"/>
-    <hyperlink r:id="rId199" ref="U73"/>
-    <hyperlink r:id="rId200" ref="V73"/>
-    <hyperlink r:id="rId201" ref="AB73"/>
-    <hyperlink r:id="rId202" ref="AC73"/>
-    <hyperlink r:id="rId203" ref="AE73"/>
-    <hyperlink r:id="rId204" ref="AG73"/>
-    <hyperlink r:id="rId205" ref="AH73"/>
-    <hyperlink r:id="rId206" ref="D74"/>
-    <hyperlink r:id="rId207" ref="G74"/>
-    <hyperlink r:id="rId208" ref="K74"/>
-    <hyperlink r:id="rId209" ref="M74"/>
-    <hyperlink r:id="rId210" ref="Q74"/>
-    <hyperlink r:id="rId211" ref="R74"/>
-    <hyperlink r:id="rId212" ref="S74"/>
-    <hyperlink r:id="rId213" ref="T74"/>
-    <hyperlink r:id="rId214" ref="U74"/>
-    <hyperlink r:id="rId215" ref="AG74"/>
-    <hyperlink r:id="rId216" ref="AH74"/>
-    <hyperlink r:id="rId217" ref="D75"/>
-    <hyperlink r:id="rId218" ref="G75"/>
-    <hyperlink r:id="rId219" ref="K75"/>
-    <hyperlink r:id="rId220" ref="M75"/>
-    <hyperlink r:id="rId221" ref="Q75"/>
-    <hyperlink r:id="rId222" ref="R75"/>
-    <hyperlink r:id="rId223" ref="S75"/>
-    <hyperlink r:id="rId224" ref="T75"/>
-    <hyperlink r:id="rId225" ref="U75"/>
-    <hyperlink r:id="rId226" ref="AB75"/>
-    <hyperlink r:id="rId227" ref="AC75"/>
-    <hyperlink r:id="rId228" ref="AE75"/>
-    <hyperlink r:id="rId229" ref="AG75"/>
-    <hyperlink r:id="rId230" ref="AH75"/>
+    <hyperlink r:id="rId66" ref="J25"/>
+    <hyperlink r:id="rId67" ref="K25"/>
+    <hyperlink r:id="rId68" ref="L25"/>
+    <hyperlink r:id="rId69" ref="M25"/>
+    <hyperlink r:id="rId70" ref="J26"/>
+    <hyperlink r:id="rId71" ref="K26"/>
+    <hyperlink r:id="rId72" ref="L26"/>
+    <hyperlink r:id="rId73" ref="M26"/>
+    <hyperlink r:id="rId74" ref="J27"/>
+    <hyperlink r:id="rId75" ref="K27"/>
+    <hyperlink r:id="rId76" ref="L27"/>
+    <hyperlink r:id="rId77" ref="M27"/>
+    <hyperlink r:id="rId78" ref="J28"/>
+    <hyperlink r:id="rId79" ref="K28"/>
+    <hyperlink r:id="rId80" ref="L28"/>
+    <hyperlink r:id="rId81" ref="M28"/>
+    <hyperlink r:id="rId82" ref="J29"/>
+    <hyperlink r:id="rId83" ref="D32"/>
+    <hyperlink r:id="rId84" ref="E32"/>
+    <hyperlink r:id="rId85" ref="D33"/>
+    <hyperlink r:id="rId86" ref="E33"/>
+    <hyperlink r:id="rId87" ref="D34"/>
+    <hyperlink r:id="rId88" ref="E34"/>
+    <hyperlink r:id="rId89" ref="D35"/>
+    <hyperlink r:id="rId90" ref="E35"/>
+    <hyperlink r:id="rId91" ref="D36"/>
+    <hyperlink r:id="rId92" ref="E36"/>
+    <hyperlink r:id="rId93" ref="D37"/>
+    <hyperlink r:id="rId94" ref="G37"/>
+    <hyperlink r:id="rId95" ref="D38"/>
+    <hyperlink r:id="rId96" ref="G38"/>
+    <hyperlink r:id="rId97" ref="D39"/>
+    <hyperlink r:id="rId98" ref="G39"/>
+    <hyperlink r:id="rId99" ref="D40"/>
+    <hyperlink r:id="rId100" ref="G40"/>
+    <hyperlink r:id="rId101" ref="D41"/>
+    <hyperlink r:id="rId102" ref="G41"/>
+    <hyperlink r:id="rId103" ref="D42"/>
+    <hyperlink r:id="rId104" ref="G42"/>
+    <hyperlink r:id="rId105" ref="R43"/>
+    <hyperlink r:id="rId106" ref="S43"/>
+    <hyperlink r:id="rId107" ref="T43"/>
+    <hyperlink r:id="rId108" ref="U43"/>
+    <hyperlink r:id="rId109" ref="R44"/>
+    <hyperlink r:id="rId110" ref="S44"/>
+    <hyperlink r:id="rId111" ref="T44"/>
+    <hyperlink r:id="rId112" ref="U44"/>
+    <hyperlink r:id="rId113" ref="R45"/>
+    <hyperlink r:id="rId114" ref="S45"/>
+    <hyperlink r:id="rId115" ref="T45"/>
+    <hyperlink r:id="rId116" ref="U45"/>
+    <hyperlink r:id="rId117" ref="V46"/>
+    <hyperlink r:id="rId118" ref="W46"/>
+    <hyperlink r:id="rId119" ref="X46"/>
+    <hyperlink r:id="rId120" ref="Y46"/>
+    <hyperlink r:id="rId121" ref="V47"/>
+    <hyperlink r:id="rId122" ref="W47"/>
+    <hyperlink r:id="rId123" ref="X47"/>
+    <hyperlink r:id="rId124" ref="Y47"/>
+    <hyperlink r:id="rId125" ref="V48"/>
+    <hyperlink r:id="rId126" ref="W48"/>
+    <hyperlink r:id="rId127" ref="X48"/>
+    <hyperlink r:id="rId128" ref="Y48"/>
+    <hyperlink r:id="rId129" ref="V49"/>
+    <hyperlink r:id="rId130" ref="W49"/>
+    <hyperlink r:id="rId131" ref="X49"/>
+    <hyperlink r:id="rId132" ref="Y49"/>
+    <hyperlink r:id="rId133" ref="V50"/>
+    <hyperlink r:id="rId134" ref="W50"/>
+    <hyperlink r:id="rId135" ref="X50"/>
+    <hyperlink r:id="rId136" ref="Y50"/>
+    <hyperlink r:id="rId137" ref="V51"/>
+    <hyperlink r:id="rId138" ref="W51"/>
+    <hyperlink r:id="rId139" ref="X51"/>
+    <hyperlink r:id="rId140" ref="Y51"/>
+    <hyperlink r:id="rId141" ref="J52"/>
+    <hyperlink r:id="rId142" ref="K52"/>
+    <hyperlink r:id="rId143" ref="M52"/>
+    <hyperlink r:id="rId144" ref="J53"/>
+    <hyperlink r:id="rId145" ref="K53"/>
+    <hyperlink r:id="rId146" ref="L53"/>
+    <hyperlink r:id="rId147" ref="M53"/>
+    <hyperlink r:id="rId148" ref="J54"/>
+    <hyperlink r:id="rId149" ref="K54"/>
+    <hyperlink r:id="rId150" ref="L54"/>
+    <hyperlink r:id="rId151" ref="M54"/>
+    <hyperlink r:id="rId152" ref="J55"/>
+    <hyperlink r:id="rId153" ref="K55"/>
+    <hyperlink r:id="rId154" ref="L55"/>
+    <hyperlink r:id="rId155" ref="M55"/>
+    <hyperlink r:id="rId156" ref="J56"/>
+    <hyperlink r:id="rId157" ref="K56"/>
+    <hyperlink r:id="rId158" ref="L56"/>
+    <hyperlink r:id="rId159" ref="M56"/>
+    <hyperlink r:id="rId160" ref="J57"/>
+    <hyperlink r:id="rId161" ref="K57"/>
+    <hyperlink r:id="rId162" ref="L57"/>
+    <hyperlink r:id="rId163" ref="M57"/>
+    <hyperlink r:id="rId164" ref="J58"/>
+    <hyperlink r:id="rId165" ref="K58"/>
+    <hyperlink r:id="rId166" ref="L58"/>
+    <hyperlink r:id="rId167" ref="M58"/>
+    <hyperlink r:id="rId168" ref="J59"/>
+    <hyperlink r:id="rId169" ref="K59"/>
+    <hyperlink r:id="rId170" ref="L59"/>
+    <hyperlink r:id="rId171" ref="M59"/>
+    <hyperlink r:id="rId172" ref="E60"/>
+    <hyperlink r:id="rId173" ref="M61"/>
+    <hyperlink r:id="rId174" ref="V61"/>
+    <hyperlink r:id="rId175" ref="W61"/>
+    <hyperlink r:id="rId176" ref="AB61"/>
+    <hyperlink r:id="rId177" ref="AC61"/>
+    <hyperlink r:id="rId178" ref="AE61"/>
+    <hyperlink r:id="rId179" ref="N63"/>
+    <hyperlink r:id="rId180" ref="AB63"/>
+    <hyperlink r:id="rId181" ref="AC63"/>
+    <hyperlink r:id="rId182" ref="AE63"/>
+    <hyperlink r:id="rId183" ref="N65"/>
+    <hyperlink r:id="rId184" ref="O65"/>
+    <hyperlink r:id="rId185" ref="P65"/>
+    <hyperlink r:id="rId186" ref="Q65"/>
+    <hyperlink r:id="rId187" ref="N66"/>
+    <hyperlink r:id="rId188" ref="O66"/>
+    <hyperlink r:id="rId189" ref="P66"/>
+    <hyperlink r:id="rId190" ref="Q66"/>
+    <hyperlink r:id="rId191" ref="AB66"/>
+    <hyperlink r:id="rId192" ref="AC66"/>
+    <hyperlink r:id="rId193" ref="N67"/>
+    <hyperlink r:id="rId194" ref="O67"/>
+    <hyperlink r:id="rId195" ref="P67"/>
+    <hyperlink r:id="rId196" ref="Q67"/>
+    <hyperlink r:id="rId197" ref="M69"/>
+    <hyperlink r:id="rId198" ref="V69"/>
+    <hyperlink r:id="rId199" ref="W69"/>
+    <hyperlink r:id="rId200" ref="Z69"/>
+    <hyperlink r:id="rId201" ref="AB69"/>
+    <hyperlink r:id="rId202" ref="AC69"/>
+    <hyperlink r:id="rId203" ref="AD69"/>
+    <hyperlink r:id="rId204" ref="AE69"/>
+    <hyperlink r:id="rId205" ref="M70"/>
+    <hyperlink r:id="rId206" ref="V70"/>
+    <hyperlink r:id="rId207" ref="W70"/>
+    <hyperlink r:id="rId208" ref="Z70"/>
+    <hyperlink r:id="rId209" ref="AB70"/>
+    <hyperlink r:id="rId210" ref="AC70"/>
+    <hyperlink r:id="rId211" ref="AD70"/>
+    <hyperlink r:id="rId212" ref="D73"/>
+    <hyperlink r:id="rId213" ref="G73"/>
+    <hyperlink r:id="rId214" ref="K73"/>
+    <hyperlink r:id="rId215" ref="M73"/>
+    <hyperlink r:id="rId216" ref="Q73"/>
+    <hyperlink r:id="rId217" ref="R73"/>
+    <hyperlink r:id="rId218" ref="S73"/>
+    <hyperlink r:id="rId219" ref="T73"/>
+    <hyperlink r:id="rId220" ref="U73"/>
+    <hyperlink r:id="rId221" ref="V73"/>
+    <hyperlink r:id="rId222" ref="AB73"/>
+    <hyperlink r:id="rId223" ref="AC73"/>
+    <hyperlink r:id="rId224" ref="AE73"/>
+    <hyperlink r:id="rId225" ref="AG73"/>
+    <hyperlink r:id="rId226" ref="AH73"/>
+    <hyperlink r:id="rId227" ref="D74"/>
+    <hyperlink r:id="rId228" ref="G74"/>
+    <hyperlink r:id="rId229" ref="K74"/>
+    <hyperlink r:id="rId230" ref="M74"/>
+    <hyperlink r:id="rId231" ref="Q74"/>
+    <hyperlink r:id="rId232" ref="R74"/>
+    <hyperlink r:id="rId233" ref="S74"/>
+    <hyperlink r:id="rId234" ref="T74"/>
+    <hyperlink r:id="rId235" ref="U74"/>
+    <hyperlink r:id="rId236" ref="V74"/>
+    <hyperlink r:id="rId237" ref="AG74"/>
+    <hyperlink r:id="rId238" ref="AH74"/>
+    <hyperlink r:id="rId239" ref="D75"/>
+    <hyperlink r:id="rId240" ref="G75"/>
+    <hyperlink r:id="rId241" ref="K75"/>
+    <hyperlink r:id="rId242" ref="M75"/>
+    <hyperlink r:id="rId243" ref="Q75"/>
+    <hyperlink r:id="rId244" ref="R75"/>
+    <hyperlink r:id="rId245" ref="S75"/>
+    <hyperlink r:id="rId246" ref="T75"/>
+    <hyperlink r:id="rId247" ref="U75"/>
+    <hyperlink r:id="rId248" ref="AB75"/>
+    <hyperlink r:id="rId249" ref="AC75"/>
+    <hyperlink r:id="rId250" ref="AE75"/>
+    <hyperlink r:id="rId251" ref="AG75"/>
+    <hyperlink r:id="rId252" ref="AH75"/>
   </hyperlinks>
-  <drawing r:id="rId231"/>
+  <drawing r:id="rId253"/>
 </worksheet>
 </file>
--- a/lg-com-status-dashboard/신호등-Article.xlsx
+++ b/lg-com-status-dashboard/신호등-Article.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="373">
   <si>
     <t>Title</t>
   </si>
@@ -5780,9 +5780,7 @@
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
-      <c r="F66" s="18" t="s">
-        <v>55</v>
-      </c>
+      <c r="F66" s="18"/>
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="9"/>
@@ -5842,9 +5840,7 @@
       </c>
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
-      <c r="F67" s="14" t="s">
-        <v>55</v>
-      </c>
+      <c r="F67" s="14"/>
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="16"/>

--- a/lg-com-status-dashboard/신호등-Article.xlsx
+++ b/lg-com-status-dashboard/신호등-Article.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="375">
   <si>
     <t>Title</t>
   </si>
@@ -944,6 +944,9 @@
     <t>How to clean MWO</t>
   </si>
   <si>
+    <t>https://www.lg.com/uk/lg-experience/helpful-hints/how-to-clean-a-microwave-without-harsh-chemicals/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/vn/lg-experience/goi-y-va-meo/cach-ve-sinh-lo-vi-song/</t>
   </si>
   <si>
@@ -969,6 +972,9 @@
   </si>
   <si>
     <t>MWO buying guide</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/uk/lg-experience/helpful-hints/microwave-size-and-buying-guide/</t>
   </si>
   <si>
     <t>https://www.lg.com/vn/lg-experience/goi-y-va-meo/huong-dan-mua-va-chon-kich-thuoc-lo-vi-song/</t>
@@ -1141,7 +1147,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm월 dd일"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="46">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1355,6 +1361,11 @@
     <font>
       <color rgb="FF000000"/>
       <name val="&quot;Microsoft GothicNeo&quot;"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -1791,7 +1802,7 @@
     <xf borderId="8" fillId="3" fontId="41" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="42" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="6" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1806,7 +1817,7 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="42" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="43" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1815,16 +1826,16 @@
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="42" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="43" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="43" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="44" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="44" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="45" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -5952,8 +5963,8 @@
       <c r="C69" s="84" t="s">
         <v>309</v>
       </c>
-      <c r="D69" s="10" t="s">
-        <v>56</v>
+      <c r="D69" s="15" t="s">
+        <v>310</v>
       </c>
       <c r="E69" s="13" t="s">
         <v>56</v>
@@ -5974,7 +5985,7 @@
       </c>
       <c r="L69" s="16"/>
       <c r="M69" s="15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N69" s="10" t="s">
         <v>56</v>
@@ -5991,28 +6002,28 @@
       <c r="T69" s="16"/>
       <c r="U69" s="16"/>
       <c r="V69" s="15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="W69" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X69" s="10"/>
       <c r="Y69" s="16"/>
       <c r="Z69" s="87" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA69" s="16"/>
       <c r="AB69" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AC69" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AD69" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AE69" s="15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF69" s="10"/>
       <c r="AG69" s="9"/>
@@ -6030,10 +6041,10 @@
         <v>308</v>
       </c>
       <c r="C70" s="84" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D70" s="88" t="s">
-        <v>56</v>
+        <v>320</v>
       </c>
       <c r="E70" s="89" t="s">
         <v>56</v>
@@ -6054,7 +6065,7 @@
       </c>
       <c r="L70" s="16"/>
       <c r="M70" s="15" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N70" s="10" t="s">
         <v>56</v>
@@ -6071,25 +6082,25 @@
       <c r="T70" s="16"/>
       <c r="U70" s="16"/>
       <c r="V70" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="W70" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="X70" s="10"/>
       <c r="Y70" s="16"/>
       <c r="Z70" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AA70" s="28"/>
       <c r="AB70" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AC70" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AD70" s="15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AE70" s="10" t="s">
         <v>56</v>
@@ -6107,10 +6118,10 @@
     <row r="71">
       <c r="A71" s="10"/>
       <c r="B71" s="84" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C71" s="84" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D71" s="90"/>
       <c r="E71" s="14"/>
@@ -6153,10 +6164,10 @@
     <row r="72">
       <c r="A72" s="10"/>
       <c r="B72" s="84" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C72" s="84" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D72" s="95"/>
       <c r="E72" s="14"/>
@@ -6199,13 +6210,13 @@
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="84" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C73" s="84" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D73" s="97" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>55</v>
@@ -6214,7 +6225,7 @@
         <v>55</v>
       </c>
       <c r="G73" s="48" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H73" s="14" t="s">
         <v>56</v>
@@ -6224,11 +6235,11 @@
         <v>55</v>
       </c>
       <c r="K73" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L73" s="98"/>
       <c r="M73" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N73" s="14" t="s">
         <v>55</v>
@@ -6236,22 +6247,22 @@
       <c r="O73" s="50"/>
       <c r="P73" s="50"/>
       <c r="Q73" s="12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="R73" s="99" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="S73" s="99" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="T73" s="48" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="U73" s="48" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="V73" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="W73" s="14"/>
       <c r="X73" s="94"/>
@@ -6261,23 +6272,23 @@
       <c r="Z73" s="94"/>
       <c r="AA73" s="91"/>
       <c r="AB73" s="48" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AC73" s="48" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AD73" s="98"/>
       <c r="AE73" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AF73" s="14" t="s">
         <v>57</v>
       </c>
       <c r="AG73" s="19" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AH73" s="19" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AI73" s="9"/>
       <c r="AJ73" s="9"/>
@@ -6289,13 +6300,13 @@
     <row r="74">
       <c r="A74" s="9"/>
       <c r="B74" s="18" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E74" s="18" t="s">
         <v>55</v>
@@ -6304,7 +6315,7 @@
         <v>55</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H74" s="18" t="s">
         <v>55</v>
@@ -6314,11 +6325,11 @@
         <v>55</v>
       </c>
       <c r="K74" s="19" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L74" s="18"/>
       <c r="M74" s="19" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N74" s="18" t="s">
         <v>55</v>
@@ -6326,22 +6337,22 @@
       <c r="O74" s="9"/>
       <c r="P74" s="9"/>
       <c r="Q74" s="19" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="R74" s="19" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="S74" s="19" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="T74" s="19" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="U74" s="19" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="V74" s="19" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="W74" s="18" t="s">
         <v>57</v>
@@ -6360,10 +6371,10 @@
         <v>57</v>
       </c>
       <c r="AG74" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AH74" s="19" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AI74" s="9"/>
       <c r="AJ74" s="9"/>
@@ -6375,13 +6386,13 @@
     <row r="75" ht="18.0" customHeight="1">
       <c r="A75" s="9"/>
       <c r="B75" s="18" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E75" s="18" t="s">
         <v>55</v>
@@ -6390,7 +6401,7 @@
         <v>55</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H75" s="18" t="s">
         <v>55</v>
@@ -6400,11 +6411,11 @@
         <v>55</v>
       </c>
       <c r="K75" s="19" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L75" s="18"/>
       <c r="M75" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N75" s="18" t="s">
         <v>55</v>
@@ -6412,19 +6423,19 @@
       <c r="O75" s="9"/>
       <c r="P75" s="9"/>
       <c r="Q75" s="19" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="R75" s="19" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="S75" s="19" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="T75" s="19" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="U75" s="19" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V75" s="18" t="s">
         <v>56</v>
@@ -6439,23 +6450,23 @@
       <c r="Z75" s="9"/>
       <c r="AA75" s="9"/>
       <c r="AB75" s="19" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AC75" s="19" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AD75" s="18"/>
       <c r="AE75" s="19" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AF75" s="18" t="s">
         <v>57</v>
       </c>
       <c r="AG75" s="19" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH75" s="19" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AI75" s="9"/>
       <c r="AJ75" s="9"/>
@@ -45515,63 +45526,65 @@
     <hyperlink r:id="rId197" ref="O67"/>
     <hyperlink r:id="rId198" ref="P67"/>
     <hyperlink r:id="rId199" ref="Q67"/>
-    <hyperlink r:id="rId200" ref="M69"/>
-    <hyperlink r:id="rId201" ref="V69"/>
-    <hyperlink r:id="rId202" ref="W69"/>
-    <hyperlink r:id="rId203" ref="Z69"/>
-    <hyperlink r:id="rId204" ref="AB69"/>
-    <hyperlink r:id="rId205" ref="AC69"/>
-    <hyperlink r:id="rId206" ref="AD69"/>
-    <hyperlink r:id="rId207" ref="AE69"/>
-    <hyperlink r:id="rId208" ref="M70"/>
-    <hyperlink r:id="rId209" ref="V70"/>
-    <hyperlink r:id="rId210" ref="W70"/>
-    <hyperlink r:id="rId211" ref="Z70"/>
-    <hyperlink r:id="rId212" ref="AB70"/>
-    <hyperlink r:id="rId213" ref="AC70"/>
-    <hyperlink r:id="rId214" ref="AD70"/>
-    <hyperlink r:id="rId215" ref="D73"/>
-    <hyperlink r:id="rId216" ref="G73"/>
-    <hyperlink r:id="rId217" ref="K73"/>
-    <hyperlink r:id="rId218" ref="M73"/>
-    <hyperlink r:id="rId219" ref="Q73"/>
-    <hyperlink r:id="rId220" ref="R73"/>
-    <hyperlink r:id="rId221" ref="S73"/>
-    <hyperlink r:id="rId222" ref="T73"/>
-    <hyperlink r:id="rId223" ref="U73"/>
-    <hyperlink r:id="rId224" ref="V73"/>
-    <hyperlink r:id="rId225" ref="AB73"/>
-    <hyperlink r:id="rId226" ref="AC73"/>
-    <hyperlink r:id="rId227" ref="AE73"/>
-    <hyperlink r:id="rId228" ref="AG73"/>
-    <hyperlink r:id="rId229" ref="AH73"/>
-    <hyperlink r:id="rId230" ref="D74"/>
-    <hyperlink r:id="rId231" ref="G74"/>
-    <hyperlink r:id="rId232" ref="K74"/>
-    <hyperlink r:id="rId233" ref="M74"/>
-    <hyperlink r:id="rId234" ref="Q74"/>
-    <hyperlink r:id="rId235" ref="R74"/>
-    <hyperlink r:id="rId236" ref="S74"/>
-    <hyperlink r:id="rId237" ref="T74"/>
-    <hyperlink r:id="rId238" ref="U74"/>
-    <hyperlink r:id="rId239" ref="V74"/>
-    <hyperlink r:id="rId240" ref="AG74"/>
-    <hyperlink r:id="rId241" ref="AH74"/>
-    <hyperlink r:id="rId242" ref="D75"/>
-    <hyperlink r:id="rId243" ref="G75"/>
-    <hyperlink r:id="rId244" ref="K75"/>
-    <hyperlink r:id="rId245" ref="M75"/>
-    <hyperlink r:id="rId246" ref="Q75"/>
-    <hyperlink r:id="rId247" ref="R75"/>
-    <hyperlink r:id="rId248" ref="S75"/>
-    <hyperlink r:id="rId249" ref="T75"/>
-    <hyperlink r:id="rId250" ref="U75"/>
-    <hyperlink r:id="rId251" ref="AB75"/>
-    <hyperlink r:id="rId252" ref="AC75"/>
-    <hyperlink r:id="rId253" ref="AE75"/>
-    <hyperlink r:id="rId254" ref="AG75"/>
-    <hyperlink r:id="rId255" ref="AH75"/>
+    <hyperlink r:id="rId200" ref="D69"/>
+    <hyperlink r:id="rId201" ref="M69"/>
+    <hyperlink r:id="rId202" ref="V69"/>
+    <hyperlink r:id="rId203" ref="W69"/>
+    <hyperlink r:id="rId204" ref="Z69"/>
+    <hyperlink r:id="rId205" ref="AB69"/>
+    <hyperlink r:id="rId206" ref="AC69"/>
+    <hyperlink r:id="rId207" ref="AD69"/>
+    <hyperlink r:id="rId208" ref="AE69"/>
+    <hyperlink r:id="rId209" ref="D70"/>
+    <hyperlink r:id="rId210" ref="M70"/>
+    <hyperlink r:id="rId211" ref="V70"/>
+    <hyperlink r:id="rId212" ref="W70"/>
+    <hyperlink r:id="rId213" ref="Z70"/>
+    <hyperlink r:id="rId214" ref="AB70"/>
+    <hyperlink r:id="rId215" ref="AC70"/>
+    <hyperlink r:id="rId216" ref="AD70"/>
+    <hyperlink r:id="rId217" ref="D73"/>
+    <hyperlink r:id="rId218" ref="G73"/>
+    <hyperlink r:id="rId219" ref="K73"/>
+    <hyperlink r:id="rId220" ref="M73"/>
+    <hyperlink r:id="rId221" ref="Q73"/>
+    <hyperlink r:id="rId222" ref="R73"/>
+    <hyperlink r:id="rId223" ref="S73"/>
+    <hyperlink r:id="rId224" ref="T73"/>
+    <hyperlink r:id="rId225" ref="U73"/>
+    <hyperlink r:id="rId226" ref="V73"/>
+    <hyperlink r:id="rId227" ref="AB73"/>
+    <hyperlink r:id="rId228" ref="AC73"/>
+    <hyperlink r:id="rId229" ref="AE73"/>
+    <hyperlink r:id="rId230" ref="AG73"/>
+    <hyperlink r:id="rId231" ref="AH73"/>
+    <hyperlink r:id="rId232" ref="D74"/>
+    <hyperlink r:id="rId233" ref="G74"/>
+    <hyperlink r:id="rId234" ref="K74"/>
+    <hyperlink r:id="rId235" ref="M74"/>
+    <hyperlink r:id="rId236" ref="Q74"/>
+    <hyperlink r:id="rId237" ref="R74"/>
+    <hyperlink r:id="rId238" ref="S74"/>
+    <hyperlink r:id="rId239" ref="T74"/>
+    <hyperlink r:id="rId240" ref="U74"/>
+    <hyperlink r:id="rId241" ref="V74"/>
+    <hyperlink r:id="rId242" ref="AG74"/>
+    <hyperlink r:id="rId243" ref="AH74"/>
+    <hyperlink r:id="rId244" ref="D75"/>
+    <hyperlink r:id="rId245" ref="G75"/>
+    <hyperlink r:id="rId246" ref="K75"/>
+    <hyperlink r:id="rId247" ref="M75"/>
+    <hyperlink r:id="rId248" ref="Q75"/>
+    <hyperlink r:id="rId249" ref="R75"/>
+    <hyperlink r:id="rId250" ref="S75"/>
+    <hyperlink r:id="rId251" ref="T75"/>
+    <hyperlink r:id="rId252" ref="U75"/>
+    <hyperlink r:id="rId253" ref="AB75"/>
+    <hyperlink r:id="rId254" ref="AC75"/>
+    <hyperlink r:id="rId255" ref="AE75"/>
+    <hyperlink r:id="rId256" ref="AG75"/>
+    <hyperlink r:id="rId257" ref="AH75"/>
   </hyperlinks>
-  <drawing r:id="rId256"/>
+  <drawing r:id="rId258"/>
 </worksheet>
 </file>